--- a/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_validada_NO_TOCAR.xlsx
+++ b/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_validada_NO_TOCAR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Raw_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="651" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{527E32A8-3B6A-4EDB-A596-CD9A7D230C11}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097920CD-50F3-44A4-9CD3-B49AA71A0C22}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E85862A8-A9B5-4BB7-B4AF-3D0252E6C1A3}"/>
+    <workbookView xWindow="14303" yWindow="-1155" windowWidth="21795" windowHeight="12975" xr2:uid="{E85862A8-A9B5-4BB7-B4AF-3D0252E6C1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -295,8 +295,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -374,7 +382,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1417,34 +1425,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}">
   <dimension ref="A1:BU73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.59765625" customWidth="1"/>
-    <col min="3" max="4" width="11.59765625" customWidth="1"/>
-    <col min="5" max="6" width="11.3984375" customWidth="1"/>
-    <col min="7" max="7" width="10.86328125" customWidth="1"/>
-    <col min="8" max="13" width="11.3984375" customWidth="1"/>
-    <col min="14" max="14" width="13.86328125" customWidth="1"/>
-    <col min="15" max="19" width="11.3984375" customWidth="1"/>
-    <col min="20" max="20" width="10.86328125" customWidth="1"/>
-    <col min="21" max="21" width="11.3984375" customWidth="1"/>
-    <col min="22" max="22" width="10.86328125" customWidth="1"/>
-    <col min="23" max="26" width="11.3984375" customWidth="1"/>
-    <col min="27" max="28" width="10.86328125" customWidth="1"/>
-    <col min="29" max="29" width="13.265625" customWidth="1"/>
-    <col min="30" max="30" width="13.59765625" customWidth="1"/>
-    <col min="31" max="34" width="11.3984375" customWidth="1"/>
-    <col min="35" max="35" width="20.59765625" bestFit="1" customWidth="1"/>
-    <col min="36" max="47" width="11.3984375" customWidth="1"/>
-    <col min="48" max="48" width="13.86328125" customWidth="1"/>
-    <col min="49" max="61" width="11.3984375" customWidth="1"/>
-    <col min="62" max="68" width="10.86328125" customWidth="1"/>
-    <col min="69" max="72" width="11.3984375" customWidth="1"/>
-    <col min="73" max="74" width="10.86328125" customWidth="1"/>
-    <col min="75" max="75" width="11.3984375" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" customWidth="1"/>
+    <col min="3" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="13" width="11.42578125" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="15" max="19" width="11.42578125" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" customWidth="1"/>
+    <col min="21" max="21" width="11.42578125" customWidth="1"/>
+    <col min="22" max="22" width="10.85546875" customWidth="1"/>
+    <col min="23" max="26" width="11.42578125" customWidth="1"/>
+    <col min="27" max="28" width="10.85546875" customWidth="1"/>
+    <col min="29" max="29" width="13.28515625" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" customWidth="1"/>
+    <col min="31" max="34" width="11.42578125" customWidth="1"/>
+    <col min="35" max="35" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="47" width="11.42578125" customWidth="1"/>
+    <col min="48" max="48" width="13.85546875" customWidth="1"/>
+    <col min="49" max="61" width="11.42578125" customWidth="1"/>
+    <col min="62" max="68" width="10.85546875" customWidth="1"/>
+    <col min="69" max="72" width="11.42578125" customWidth="1"/>
+    <col min="73" max="74" width="10.85546875" customWidth="1"/>
+    <col min="75" max="75" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="C1">
         <v>1</v>
       </c>
@@ -1659,7 +1667,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:73" ht="57" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:73" ht="60" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>59</v>
       </c>
@@ -1877,14 +1885,14 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
       <c r="G3" s="1"/>
@@ -1915,13 +1923,13 @@
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AL3" s="1"/>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8"/>
-      <c r="AQ3" s="8"/>
-      <c r="AR3" s="8"/>
-      <c r="AS3" s="8"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
       <c r="AT3" s="1"/>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
@@ -1951,7 +1959,7 @@
       <c r="BT3" s="1"/>
       <c r="BU3" s="1"/>
     </row>
-    <row r="4" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1960,11 +1968,15 @@
       </c>
       <c r="E4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -1987,13 +1999,13 @@
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AL4" s="1"/>
-      <c r="AM4" s="8"/>
-      <c r="AN4" s="8"/>
-      <c r="AO4" s="8"/>
-      <c r="AP4" s="8"/>
-      <c r="AQ4" s="8"/>
-      <c r="AR4" s="8"/>
-      <c r="AS4" s="8"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1"/>
+      <c r="AS4" s="1"/>
       <c r="AT4" s="1"/>
       <c r="AU4" s="1"/>
       <c r="AV4" s="1"/>
@@ -2023,7 +2035,7 @@
       <c r="BT4" s="1"/>
       <c r="BU4" s="1"/>
     </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2178,7 +2190,7 @@
       </c>
       <c r="BU5" s="2"/>
     </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2210,7 +2222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2218,7 +2230,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2289,7 +2301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2380,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2491,7 +2503,7 @@
       <c r="BT11" s="2"/>
       <c r="BU11" s="2"/>
     </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2562,7 +2574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2579,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2587,7 +2599,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2598,7 +2610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2689,7 +2701,7 @@
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
     </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -2798,7 +2810,7 @@
       <c r="BT17" s="2"/>
       <c r="BU17" s="2"/>
     </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -2818,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -2847,7 +2859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -2855,7 +2867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -2869,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -2877,7 +2889,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>21</v>
       </c>
@@ -2900,7 +2912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -2981,7 +2993,7 @@
       <c r="BT24" s="2"/>
       <c r="BU24" s="2"/>
     </row>
-    <row r="25" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>23</v>
       </c>
@@ -2989,7 +3001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>24</v>
       </c>
@@ -3068,7 +3080,7 @@
       <c r="BT26" s="2"/>
       <c r="BU26" s="2"/>
     </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -3147,7 +3159,7 @@
       <c r="BT27" s="2"/>
       <c r="BU27" s="2"/>
     </row>
-    <row r="28" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26</v>
       </c>
@@ -3228,7 +3240,7 @@
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
     </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -3309,7 +3321,7 @@
       <c r="BT29" s="2"/>
       <c r="BU29" s="2"/>
     </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -3317,7 +3329,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>29</v>
       </c>
@@ -3422,7 +3434,7 @@
       <c r="BT31" s="3"/>
       <c r="BU31" s="3"/>
     </row>
-    <row r="32" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30</v>
       </c>
@@ -3509,7 +3521,7 @@
       <c r="BT32" s="2"/>
       <c r="BU32" s="2"/>
     </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -3596,7 +3608,7 @@
       <c r="BT33" s="2"/>
       <c r="BU33" s="2"/>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -3631,7 +3643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -3651,7 +3663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -3674,7 +3686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -3694,7 +3706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>36</v>
       </c>
@@ -3702,7 +3714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -3833,7 +3845,7 @@
       <c r="BT39" s="2"/>
       <c r="BU39" s="2"/>
     </row>
-    <row r="40" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -3850,7 +3862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -3891,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40</v>
       </c>
@@ -3980,7 +3992,7 @@
       <c r="BT42" s="3"/>
       <c r="BU42" s="3"/>
     </row>
-    <row r="43" spans="1:73" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:73" ht="30" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -4002,7 +4014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -4022,7 +4034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>43</v>
       </c>
@@ -4042,7 +4054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>44</v>
       </c>
@@ -4163,7 +4175,7 @@
       <c r="BT46" s="5"/>
       <c r="BU46" s="5"/>
     </row>
-    <row r="47" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>45</v>
       </c>
@@ -4248,7 +4260,7 @@
       <c r="BT47" s="3"/>
       <c r="BU47" s="3"/>
     </row>
-    <row r="48" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>46</v>
       </c>
@@ -4335,7 +4347,7 @@
       <c r="BT48" s="2"/>
       <c r="BU48" s="2"/>
     </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -4442,7 +4454,7 @@
       <c r="BT49" s="2"/>
       <c r="BU49" s="2"/>
     </row>
-    <row r="50" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>48</v>
       </c>
@@ -4521,7 +4533,7 @@
       <c r="BT50" s="3"/>
       <c r="BU50" s="3"/>
     </row>
-    <row r="51" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -4630,7 +4642,7 @@
       <c r="BT51" s="2"/>
       <c r="BU51" s="2"/>
     </row>
-    <row r="52" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -4653,7 +4665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -4667,7 +4679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>52</v>
       </c>
@@ -4752,7 +4764,7 @@
       <c r="BT54" s="3"/>
       <c r="BU54" s="3"/>
     </row>
-    <row r="55" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -4855,7 +4867,7 @@
       <c r="BT55" s="2"/>
       <c r="BU55" s="2"/>
     </row>
-    <row r="56" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -4869,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>55</v>
       </c>
@@ -4910,7 +4922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>56</v>
       </c>
@@ -4989,7 +5001,7 @@
       <c r="BT58" s="2"/>
       <c r="BU58" s="2"/>
     </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
@@ -5074,7 +5086,7 @@
       <c r="BT59" s="2"/>
       <c r="BU59" s="2"/>
     </row>
-    <row r="60" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>58</v>
       </c>
@@ -5155,7 +5167,7 @@
       <c r="BT60" s="3"/>
       <c r="BU60" s="3"/>
     </row>
-    <row r="61" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -5163,7 +5175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>60</v>
       </c>
@@ -5246,7 +5258,7 @@
       <c r="BT62" s="3"/>
       <c r="BU62" s="3"/>
     </row>
-    <row r="63" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
@@ -5327,7 +5339,7 @@
       <c r="BT63" s="2"/>
       <c r="BU63" s="2"/>
     </row>
-    <row r="64" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
@@ -5350,7 +5362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>63</v>
       </c>
@@ -5358,7 +5370,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -5437,7 +5449,7 @@
       <c r="BT66" s="2"/>
       <c r="BU66" s="2"/>
     </row>
-    <row r="67" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -5445,7 +5457,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -5453,7 +5465,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="69" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -5464,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>68</v>
       </c>
@@ -5490,7 +5502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>69</v>
       </c>
@@ -5583,7 +5595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:73" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -5668,7 +5680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:73" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>71</v>
       </c>
@@ -5806,8 +5818,8 @@
     <cfRule type="duplicateValues" dxfId="50" priority="1590"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:D37">
-    <cfRule type="duplicateValues" dxfId="49" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:D46">
     <cfRule type="duplicateValues" dxfId="47" priority="1591"/>
@@ -5819,8 +5831,8 @@
     <cfRule type="duplicateValues" dxfId="45" priority="1593"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49:D52">
-    <cfRule type="duplicateValues" dxfId="44" priority="1568"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1570"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="1568"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B53:D53">
     <cfRule type="duplicateValues" dxfId="42" priority="1594"/>
@@ -5862,19 +5874,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F02EE0-40BA-4311-B39A-384F2CBD26CC}">
   <dimension ref="A1:BT72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.59765625" customWidth="1"/>
-    <col min="32" max="32" width="13.86328125" customWidth="1"/>
-    <col min="53" max="53" width="13.86328125" customWidth="1"/>
-    <col min="57" max="60" width="10.86328125" customWidth="1"/>
-    <col min="61" max="61" width="13.59765625" customWidth="1"/>
-    <col min="62" max="62" width="13.265625" customWidth="1"/>
-    <col min="63" max="63" width="13.3984375" customWidth="1"/>
-    <col min="64" max="73" width="10.86328125" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="32" max="32" width="13.85546875" customWidth="1"/>
+    <col min="53" max="53" width="13.85546875" customWidth="1"/>
+    <col min="57" max="60" width="10.85546875" customWidth="1"/>
+    <col min="61" max="61" width="13.5703125" customWidth="1"/>
+    <col min="62" max="62" width="13.28515625" customWidth="1"/>
+    <col min="63" max="63" width="13.42578125" customWidth="1"/>
+    <col min="64" max="73" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="57.4" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:72" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6089,7 +6101,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
@@ -6259,7 +6271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6306,7 +6318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -6344,7 +6356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -6373,7 +6385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -6393,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -6505,7 +6517,7 @@
       </c>
       <c r="BT7" s="2"/>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -6597,7 +6609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6650,7 +6662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6667,7 +6679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -6696,7 +6708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:72" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:72" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
@@ -6788,7 +6800,7 @@
       <c r="BS12" s="3"/>
       <c r="BT12" s="3"/>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -6908,7 +6920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -6988,7 +7000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -7065,7 +7077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -7082,7 +7094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -7102,12 +7114,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -7166,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -7192,7 +7204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>64</v>
       </c>
@@ -7272,7 +7284,7 @@
       <c r="BS21" s="3"/>
       <c r="BT21" s="3"/>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -7380,12 +7392,12 @@
       <c r="BS22" s="2"/>
       <c r="BT22" s="2"/>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>69</v>
       </c>
@@ -7465,7 +7477,7 @@
       <c r="BS24" s="3"/>
       <c r="BT24" s="3"/>
     </row>
-    <row r="25" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -7577,7 +7589,7 @@
       <c r="BS25" s="2"/>
       <c r="BT25" s="2"/>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -7685,7 +7697,7 @@
       <c r="BS26" s="2"/>
       <c r="BT26" s="2"/>
     </row>
-    <row r="27" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
@@ -7761,7 +7773,7 @@
       <c r="BS27" s="3"/>
       <c r="BT27" s="3"/>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -7845,7 +7857,7 @@
       <c r="BS28" s="2"/>
       <c r="BT28" s="2"/>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -7853,7 +7865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
@@ -7929,7 +7941,7 @@
       <c r="BS30" s="3"/>
       <c r="BT30" s="3"/>
     </row>
-    <row r="31" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>23</v>
       </c>
@@ -8013,7 +8025,7 @@
       <c r="BS31" s="2"/>
       <c r="BT31" s="2"/>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>24</v>
       </c>
@@ -8101,7 +8113,7 @@
       <c r="BS32" s="2"/>
       <c r="BT32" s="2"/>
     </row>
-    <row r="33" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -8124,7 +8136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -8144,7 +8156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>27</v>
       </c>
@@ -8234,7 +8246,7 @@
       <c r="BS35" s="2"/>
       <c r="BT35" s="2"/>
     </row>
-    <row r="36" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>73</v>
       </c>
@@ -8316,7 +8328,7 @@
       <c r="BS36" s="3"/>
       <c r="BT36" s="3"/>
     </row>
-    <row r="37" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>28</v>
       </c>
@@ -8404,7 +8416,7 @@
       <c r="BS37" s="2"/>
       <c r="BT37" s="2"/>
     </row>
-    <row r="38" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -8427,7 +8439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -8435,7 +8447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -8519,7 +8531,7 @@
       <c r="BS40" s="3"/>
       <c r="BT40" s="3"/>
     </row>
-    <row r="41" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -8533,7 +8545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -8547,7 +8559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -8561,7 +8573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>34</v>
       </c>
@@ -8647,7 +8659,7 @@
       <c r="BS44" s="5"/>
       <c r="BT44" s="5"/>
     </row>
-    <row r="45" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -8741,7 +8753,7 @@
       <c r="BS45" s="3"/>
       <c r="BT45" s="3"/>
     </row>
-    <row r="46" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
@@ -8833,7 +8845,7 @@
       <c r="BS46" s="2"/>
       <c r="BT46" s="2"/>
     </row>
-    <row r="47" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
@@ -8917,7 +8929,7 @@
       <c r="BS47" s="2"/>
       <c r="BT47" s="2"/>
     </row>
-    <row r="48" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
@@ -8997,7 +9009,7 @@
       <c r="BS48" s="3"/>
       <c r="BT48" s="3"/>
     </row>
-    <row r="49" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>37</v>
       </c>
@@ -9083,12 +9095,12 @@
       <c r="BS49" s="2"/>
       <c r="BT49" s="2"/>
     </row>
-    <row r="50" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -9096,7 +9108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
@@ -9172,7 +9184,7 @@
       <c r="BS52" s="3"/>
       <c r="BT52" s="3"/>
     </row>
-    <row r="53" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
@@ -9248,7 +9260,7 @@
       <c r="BS53" s="2"/>
       <c r="BT53" s="2"/>
     </row>
-    <row r="54" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -9256,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -9267,7 +9279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>43</v>
       </c>
@@ -9353,7 +9365,7 @@
       <c r="BS56" s="2"/>
       <c r="BT56" s="2"/>
     </row>
-    <row r="57" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>45</v>
       </c>
@@ -9429,7 +9441,7 @@
       <c r="BS57" s="2"/>
       <c r="BT57" s="2"/>
     </row>
-    <row r="58" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>46</v>
       </c>
@@ -9505,12 +9517,12 @@
       <c r="BS58" s="3"/>
       <c r="BT58" s="3"/>
     </row>
-    <row r="59" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>48</v>
       </c>
@@ -9588,7 +9600,7 @@
       <c r="BS60" s="3"/>
       <c r="BT60" s="3"/>
     </row>
-    <row r="61" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>49</v>
       </c>
@@ -9666,7 +9678,7 @@
       <c r="BS61" s="2"/>
       <c r="BT61" s="2"/>
     </row>
-    <row r="62" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -9674,17 +9686,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
@@ -9770,27 +9782,27 @@
       <c r="BS65" s="2"/>
       <c r="BT65" s="2"/>
     </row>
-    <row r="66" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>57</v>
       </c>
@@ -9872,7 +9884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:72" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:72" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>58</v>
       </c>
@@ -9948,7 +9960,7 @@
       <c r="BS71" s="2"/>
       <c r="BT71" s="2"/>
     </row>
-    <row r="72" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>68</v>
       </c>

--- a/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_validada_NO_TOCAR.xlsx
+++ b/Modelo/datos/Raw_Data/Matriz_de_Adyacencia_Pensiones_validada_NO_TOCAR.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21a7d57e8591b932/Escritorio/CICS/2025/Tesis/Objetivos de Aprendizaje/Modelo/datos/Raw_Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="654" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{097920CD-50F3-44A4-9CD3-B49AA71A0C22}"/>
+  <xr:revisionPtr revIDLastSave="731" documentId="8_{00D88C31-2993-4F88-955D-B3AEA2AC3E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1132680C-B18F-46AF-8A73-FE00E264CF0F}"/>
   <bookViews>
-    <workbookView xWindow="14303" yWindow="-1155" windowWidth="21795" windowHeight="12975" xr2:uid="{E85862A8-A9B5-4BB7-B4AF-3D0252E6C1A3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{E85862A8-A9B5-4BB7-B4AF-3D0252E6C1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$BU$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$BR$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +39,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Camila Utreras</author>
+  </authors>
+  <commentList>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{F3444423-C88A-49F6-B3DD-93D5713E900D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Camila Utreras:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Se sugiere unir con la definición de SCOMP</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="83">
   <si>
     <t>Que_es_pension</t>
   </si>
@@ -295,7 +329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,8 +345,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +369,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -367,7 +426,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -385,11 +444,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="69">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -782,36 +863,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1101,10 +1152,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1423,36 +1470,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}">
-  <dimension ref="A1:BU73"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}">
+  <dimension ref="A1:BR70"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" customWidth="1"/>
-    <col min="3" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="13" width="11.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" customWidth="1"/>
-    <col min="15" max="19" width="11.42578125" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" customWidth="1"/>
-    <col min="23" max="26" width="11.42578125" customWidth="1"/>
-    <col min="27" max="28" width="10.85546875" customWidth="1"/>
-    <col min="29" max="29" width="13.28515625" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" customWidth="1"/>
-    <col min="31" max="34" width="11.42578125" customWidth="1"/>
-    <col min="35" max="35" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="47" width="11.42578125" customWidth="1"/>
-    <col min="48" max="48" width="13.85546875" customWidth="1"/>
-    <col min="49" max="61" width="11.42578125" customWidth="1"/>
-    <col min="62" max="68" width="10.85546875" customWidth="1"/>
-    <col min="69" max="72" width="11.42578125" customWidth="1"/>
-    <col min="73" max="74" width="10.85546875" customWidth="1"/>
-    <col min="75" max="75" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" customWidth="1"/>
+    <col min="3" max="4" width="11.59765625" customWidth="1"/>
+    <col min="5" max="6" width="11.3984375" customWidth="1"/>
+    <col min="7" max="7" width="10.86328125" customWidth="1"/>
+    <col min="8" max="13" width="11.3984375" customWidth="1"/>
+    <col min="14" max="14" width="13.86328125" customWidth="1"/>
+    <col min="15" max="18" width="11.3984375" customWidth="1"/>
+    <col min="19" max="19" width="10.86328125" customWidth="1"/>
+    <col min="20" max="20" width="11.3984375" customWidth="1"/>
+    <col min="21" max="21" width="10.86328125" customWidth="1"/>
+    <col min="22" max="23" width="11.3984375" customWidth="1"/>
+    <col min="24" max="25" width="10.86328125" customWidth="1"/>
+    <col min="26" max="26" width="13.265625" customWidth="1"/>
+    <col min="27" max="27" width="13.59765625" customWidth="1"/>
+    <col min="28" max="31" width="11.3984375" customWidth="1"/>
+    <col min="32" max="32" width="20.59765625" bestFit="1" customWidth="1"/>
+    <col min="33" max="44" width="11.3984375" customWidth="1"/>
+    <col min="45" max="45" width="13.86328125" customWidth="1"/>
+    <col min="46" max="58" width="11.3984375" customWidth="1"/>
+    <col min="59" max="65" width="10.86328125" customWidth="1"/>
+    <col min="66" max="69" width="11.3984375" customWidth="1"/>
+    <col min="70" max="71" width="10.86328125" customWidth="1"/>
+    <col min="72" max="72" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.45">
       <c r="C1">
         <v>1</v>
       </c>
@@ -1483,191 +1530,182 @@
       <c r="L1" s="7">
         <v>10</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="9">
         <v>11</v>
       </c>
-      <c r="N1">
+      <c r="N1" s="9">
         <v>12</v>
       </c>
-      <c r="O1">
-        <v>13</v>
-      </c>
-      <c r="P1">
+      <c r="O1" s="9">
         <v>14</v>
       </c>
-      <c r="Q1">
+      <c r="P1" s="9">
         <v>15</v>
       </c>
-      <c r="R1">
+      <c r="Q1" s="10">
         <v>16</v>
       </c>
-      <c r="S1">
+      <c r="R1" s="9">
         <v>17</v>
       </c>
-      <c r="T1">
+      <c r="S1" s="9">
         <v>18</v>
       </c>
-      <c r="U1">
+      <c r="T1" s="9">
         <v>19</v>
       </c>
-      <c r="V1">
+      <c r="U1" s="9">
         <v>20</v>
       </c>
-      <c r="W1">
+      <c r="V1" s="9">
         <v>21</v>
       </c>
-      <c r="X1">
-        <v>22</v>
-      </c>
-      <c r="Y1">
-        <v>23</v>
+      <c r="W1" s="9">
+        <v>24</v>
+      </c>
+      <c r="X1" s="9">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="9">
+        <v>26</v>
       </c>
       <c r="Z1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA1">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AB1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AC1">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AE1">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF1">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AG1">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AH1">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AI1">
-        <v>33</v>
-      </c>
-      <c r="AJ1">
-        <v>34</v>
-      </c>
-      <c r="AK1">
-        <v>35</v>
-      </c>
-      <c r="AL1">
         <v>36</v>
       </c>
+      <c r="AJ1" s="7">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="7">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="7">
+        <v>39</v>
+      </c>
       <c r="AM1" s="7">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AN1" s="7">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AO1" s="7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AP1" s="7">
-        <v>40</v>
-      </c>
-      <c r="AQ1" s="7">
-        <v>41</v>
-      </c>
-      <c r="AR1" s="7">
-        <v>42</v>
-      </c>
-      <c r="AS1" s="7">
         <v>43</v>
       </c>
+      <c r="AQ1">
+        <v>44</v>
+      </c>
+      <c r="AR1">
+        <v>45</v>
+      </c>
+      <c r="AS1">
+        <v>46</v>
+      </c>
       <c r="AT1">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AU1">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="AV1">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AW1">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AX1">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AY1">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AZ1">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="BA1">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="BB1">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="BC1">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="BD1">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="BE1">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="BF1">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="BG1">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="BH1">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="BI1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="BJ1">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="BK1">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="BL1">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="BM1">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="BN1">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="BO1">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="BP1">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="BQ1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="BR1">
-        <v>68</v>
-      </c>
-      <c r="BS1">
-        <v>69</v>
-      </c>
-      <c r="BT1">
-        <v>70</v>
-      </c>
-      <c r="BU1">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:73" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" ht="57" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>59</v>
       </c>
@@ -1708,184 +1746,175 @@
         <v>41</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AG2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="AE2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>79</v>
+      </c>
       <c r="AH2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK2" t="s">
         <v>80</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="AJ2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL2" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="AM2" s="6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN2" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AO2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="AS2" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AQ2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="AT2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="BS2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="BT2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="BU2" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1919,9 +1948,9 @@
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
       <c r="AM3" s="1"/>
       <c r="AN3" s="1"/>
@@ -1955,11 +1984,8 @@
       <c r="BP3" s="1"/>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="1"/>
-      <c r="BS3" s="1"/>
-      <c r="BT3" s="1"/>
-      <c r="BU3" s="1"/>
-    </row>
-    <row r="4" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1982,7 +2008,9 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
+      <c r="R4" s="1">
+        <v>1</v>
+      </c>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -1995,9 +2023,9 @@
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="1"/>
@@ -2031,11 +2059,8 @@
       <c r="BP4" s="1"/>
       <c r="BQ4" s="1"/>
       <c r="BR4" s="1"/>
-      <c r="BS4" s="1"/>
-      <c r="BT4" s="1"/>
-      <c r="BU4" s="1"/>
-    </row>
-    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2056,68 +2081,48 @@
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2">
-        <v>1</v>
-      </c>
-      <c r="O5" s="2">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2">
-        <v>1</v>
-      </c>
-      <c r="S5" s="2">
-        <v>1</v>
-      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-      <c r="U5" s="2">
-        <v>1</v>
-      </c>
+      <c r="U5" s="2"/>
       <c r="V5" s="2"/>
-      <c r="W5" s="2">
-        <v>1</v>
-      </c>
-      <c r="X5" s="2">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>1</v>
-      </c>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
       <c r="AB5" s="2">
         <v>1</v>
       </c>
-      <c r="AC5" s="2"/>
+      <c r="AC5" s="2">
+        <v>1</v>
+      </c>
       <c r="AD5" s="2"/>
-      <c r="AE5" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="2">
-        <v>1</v>
-      </c>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
       <c r="AG5" s="2"/>
       <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
+      <c r="AI5" s="2">
+        <v>1</v>
+      </c>
       <c r="AJ5" s="2"/>
       <c r="AK5" s="2"/>
-      <c r="AL5" s="2">
-        <v>1</v>
-      </c>
+      <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
       <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
-      <c r="AR5" s="2"/>
+      <c r="AQ5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="2">
+        <v>1</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2">
         <v>1</v>
@@ -2125,72 +2130,65 @@
       <c r="AU5" s="2">
         <v>1</v>
       </c>
-      <c r="AV5" s="2"/>
+      <c r="AV5" s="2">
+        <v>1</v>
+      </c>
       <c r="AW5" s="2">
         <v>1</v>
       </c>
       <c r="AX5" s="2">
         <v>1</v>
       </c>
-      <c r="AY5" s="2">
-        <v>1</v>
-      </c>
+      <c r="AY5" s="2"/>
       <c r="AZ5" s="2">
         <v>1</v>
       </c>
       <c r="BA5" s="2">
         <v>1</v>
       </c>
-      <c r="BB5" s="2"/>
+      <c r="BB5" s="2">
+        <v>1</v>
+      </c>
       <c r="BC5" s="2">
         <v>1</v>
       </c>
       <c r="BD5" s="2">
         <v>1</v>
       </c>
-      <c r="BE5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF5" s="2">
-        <v>1</v>
-      </c>
+      <c r="BE5" s="2"/>
+      <c r="BF5" s="2"/>
       <c r="BG5" s="2">
         <v>1</v>
       </c>
-      <c r="BH5" s="2"/>
-      <c r="BI5" s="2"/>
+      <c r="BH5" s="2">
+        <v>1</v>
+      </c>
+      <c r="BI5" s="2">
+        <v>1</v>
+      </c>
       <c r="BJ5" s="2">
         <v>1</v>
       </c>
-      <c r="BK5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL5" s="2">
-        <v>1</v>
-      </c>
+      <c r="BK5" s="2"/>
+      <c r="BL5" s="2"/>
       <c r="BM5" s="2">
         <v>1</v>
       </c>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
+      <c r="BN5" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO5" s="2">
+        <v>1</v>
+      </c>
       <c r="BP5" s="2">
         <v>1</v>
       </c>
       <c r="BQ5" s="2">
         <v>1</v>
       </c>
-      <c r="BR5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT5" s="2">
-        <v>1</v>
-      </c>
-      <c r="BU5" s="2"/>
-    </row>
-    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BR5" s="2"/>
+    </row>
+    <row r="6" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2203,26 +2201,20 @@
       <c r="I6">
         <v>1</v>
       </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
-        <v>1</v>
-      </c>
-      <c r="AF6">
-        <v>1</v>
-      </c>
-      <c r="AN6">
-        <v>1</v>
-      </c>
-      <c r="AV6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AS6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>5</v>
       </c>
@@ -2230,7 +2222,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>6</v>
       </c>
@@ -2252,56 +2244,41 @@
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
       <c r="AA8">
         <v>1</v>
       </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AL8">
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AQ8">
         <v>1</v>
       </c>
       <c r="AT8">
         <v>1</v>
       </c>
+      <c r="AV8">
+        <v>1</v>
+      </c>
       <c r="AW8">
         <v>1</v>
       </c>
-      <c r="AY8">
-        <v>1</v>
-      </c>
       <c r="AZ8">
         <v>1</v>
       </c>
-      <c r="BC8">
-        <v>1</v>
-      </c>
-      <c r="BK8">
-        <v>1</v>
-      </c>
-      <c r="BR8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="BH8">
+        <v>1</v>
+      </c>
+      <c r="BO8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2314,22 +2291,22 @@
       <c r="J9">
         <v>1</v>
       </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
       <c r="Q9">
         <v>1</v>
       </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9">
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
         <v>1</v>
       </c>
       <c r="AL9">
@@ -2347,52 +2324,40 @@
       <c r="AP9">
         <v>1</v>
       </c>
-      <c r="AQ9">
-        <v>1</v>
-      </c>
-      <c r="AR9">
-        <v>1</v>
-      </c>
-      <c r="AS9">
+      <c r="AT9">
+        <v>1</v>
+      </c>
+      <c r="AV9">
         <v>1</v>
       </c>
       <c r="AW9">
         <v>1</v>
       </c>
-      <c r="AY9">
-        <v>1</v>
-      </c>
       <c r="AZ9">
         <v>1</v>
       </c>
-      <c r="BC9">
-        <v>1</v>
-      </c>
-      <c r="BS9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="BP9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="AF10">
-        <v>1</v>
-      </c>
-      <c r="AL10">
-        <v>1</v>
-      </c>
-      <c r="AY10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AV10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2417,16 +2382,12 @@
       <c r="L11" s="2">
         <v>1</v>
       </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2">
-        <v>1</v>
-      </c>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
@@ -2437,15 +2398,13 @@
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
-      <c r="AA11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2">
+        <v>1</v>
+      </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
-      <c r="AE11" s="2">
-        <v>1</v>
-      </c>
+      <c r="AE11" s="2"/>
       <c r="AF11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AH11" s="2"/>
@@ -2457,89 +2416,80 @@
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
       <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
+      <c r="AQ11" s="2">
+        <v>1</v>
+      </c>
       <c r="AR11" s="2"/>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2">
         <v>1</v>
       </c>
       <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2">
-        <v>1</v>
-      </c>
+      <c r="AV11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
-      <c r="AY11" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ11" s="2"/>
+      <c r="AY11" s="2"/>
+      <c r="AZ11" s="2">
+        <v>1</v>
+      </c>
       <c r="BA11" s="2"/>
       <c r="BB11" s="2"/>
-      <c r="BC11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="2"/>
+      <c r="BC11" s="2"/>
+      <c r="BD11" s="2">
+        <v>1</v>
+      </c>
       <c r="BE11" s="2"/>
       <c r="BF11" s="2"/>
       <c r="BG11" s="2">
         <v>1</v>
       </c>
       <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2">
-        <v>1</v>
-      </c>
+      <c r="BI11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BJ11" s="2"/>
       <c r="BK11" s="2"/>
-      <c r="BL11" s="2">
-        <v>1</v>
-      </c>
+      <c r="BL11" s="2"/>
       <c r="BM11" s="2"/>
       <c r="BN11" s="2"/>
       <c r="BO11" s="2"/>
       <c r="BP11" s="2"/>
       <c r="BQ11" s="2"/>
       <c r="BR11" s="2"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
-      <c r="BU11" s="2"/>
-    </row>
-    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="AA12">
+      <c r="AD12">
         <v>1</v>
       </c>
       <c r="AG12">
         <v>1</v>
       </c>
-      <c r="AJ12">
-        <v>1</v>
-      </c>
-      <c r="AL12">
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
+      <c r="AR12">
+        <v>1</v>
+      </c>
+      <c r="AS12">
         <v>1</v>
       </c>
       <c r="AT12">
         <v>1</v>
       </c>
-      <c r="AU12">
-        <v>1</v>
-      </c>
       <c r="AV12">
         <v>1</v>
       </c>
@@ -2549,19 +2499,16 @@
       <c r="AY12">
         <v>1</v>
       </c>
-      <c r="AZ12">
-        <v>1</v>
-      </c>
       <c r="BB12">
         <v>1</v>
       </c>
+      <c r="BD12">
+        <v>1</v>
+      </c>
       <c r="BE12">
         <v>1</v>
       </c>
-      <c r="BG12">
-        <v>1</v>
-      </c>
-      <c r="BH12">
+      <c r="BF12">
         <v>1</v>
       </c>
       <c r="BI12">
@@ -2570,28 +2517,28 @@
       <c r="BL12">
         <v>1</v>
       </c>
-      <c r="BO12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="AB13">
-        <v>1</v>
-      </c>
-      <c r="AC13">
-        <v>1</v>
-      </c>
-      <c r="BQ13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="BN13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2599,325 +2546,370 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="BM15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
+        <v>1</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>1</v>
+      </c>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3"/>
+      <c r="AU15" s="3"/>
+      <c r="AV15" s="3"/>
+      <c r="AW15" s="3"/>
+      <c r="AX15" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY15" s="3"/>
+      <c r="AZ15" s="3"/>
+      <c r="BA15" s="3"/>
+      <c r="BB15" s="3"/>
+      <c r="BC15" s="3"/>
+      <c r="BD15" s="3"/>
+      <c r="BE15" s="3"/>
+      <c r="BF15" s="3"/>
+      <c r="BG15" s="3"/>
+      <c r="BH15" s="3"/>
+      <c r="BI15" s="3"/>
+      <c r="BJ15" s="3"/>
+      <c r="BK15" s="3"/>
+      <c r="BL15" s="3"/>
+      <c r="BM15" s="3"/>
+      <c r="BN15" s="3"/>
+      <c r="BO15" s="3"/>
+      <c r="BP15" s="3"/>
+      <c r="BQ15" s="3"/>
+      <c r="BR15" s="3"/>
+    </row>
+    <row r="16" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3">
-        <v>1</v>
-      </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3">
-        <v>1</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3"/>
-      <c r="AS16" s="3"/>
-      <c r="AT16" s="3"/>
-      <c r="AU16" s="3">
-        <v>1</v>
-      </c>
-      <c r="AV16" s="3"/>
-      <c r="AW16" s="3"/>
-      <c r="AX16" s="3"/>
-      <c r="AY16" s="3"/>
-      <c r="AZ16" s="3"/>
-      <c r="BA16" s="3">
-        <v>1</v>
-      </c>
-      <c r="BB16" s="3"/>
-      <c r="BC16" s="3"/>
-      <c r="BD16" s="3"/>
-      <c r="BE16" s="3"/>
-      <c r="BF16" s="3"/>
-      <c r="BG16" s="3"/>
-      <c r="BH16" s="3"/>
-      <c r="BI16" s="3"/>
-      <c r="BJ16" s="3"/>
-      <c r="BK16" s="3"/>
-      <c r="BL16" s="3"/>
-      <c r="BM16" s="3"/>
-      <c r="BN16" s="3"/>
-      <c r="BO16" s="3"/>
-      <c r="BP16" s="3"/>
-      <c r="BQ16" s="3"/>
-      <c r="BR16" s="3"/>
-      <c r="BS16" s="3"/>
-      <c r="BT16" s="3"/>
-      <c r="BU16" s="3"/>
-    </row>
-    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2">
-        <v>1</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2">
-        <v>1</v>
-      </c>
-      <c r="S17" s="2">
-        <v>1</v>
-      </c>
-      <c r="T17" s="2">
-        <v>1</v>
-      </c>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
-      <c r="AL17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AP17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS17" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT17" s="2"/>
-      <c r="AU17" s="2"/>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2"/>
-      <c r="AY17" s="2"/>
-      <c r="AZ17" s="2"/>
-      <c r="BA17" s="2"/>
-      <c r="BB17" s="2"/>
-      <c r="BC17" s="2"/>
-      <c r="BD17" s="2"/>
-      <c r="BE17" s="2"/>
-      <c r="BF17" s="2"/>
-      <c r="BG17" s="2"/>
-      <c r="BH17" s="2"/>
-      <c r="BI17" s="2"/>
-      <c r="BJ17" s="2"/>
-      <c r="BK17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BL17" s="2"/>
-      <c r="BM17" s="2"/>
-      <c r="BN17" s="2"/>
-      <c r="BO17" s="2"/>
-      <c r="BP17" s="2"/>
-      <c r="BQ17" s="2"/>
-      <c r="BR17" s="2"/>
-      <c r="BS17" s="2"/>
-      <c r="BT17" s="2"/>
-      <c r="BU17" s="2"/>
-    </row>
-    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+      <c r="AH16" s="2"/>
+      <c r="AI16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="2"/>
+      <c r="AK16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ16" s="2"/>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2"/>
+      <c r="AT16" s="2"/>
+      <c r="AU16" s="2"/>
+      <c r="AV16" s="2"/>
+      <c r="AW16" s="2"/>
+      <c r="AX16" s="2"/>
+      <c r="AY16" s="2"/>
+      <c r="AZ16" s="2"/>
+      <c r="BA16" s="2"/>
+      <c r="BB16" s="2"/>
+      <c r="BC16" s="2"/>
+      <c r="BD16" s="2"/>
+      <c r="BE16" s="2"/>
+      <c r="BF16" s="2"/>
+      <c r="BG16" s="2"/>
+      <c r="BH16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BI16" s="2"/>
+      <c r="BJ16" s="2"/>
+      <c r="BK16" s="2"/>
+      <c r="BL16" s="2"/>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="2"/>
+      <c r="BO16" s="2"/>
+      <c r="BP16" s="2"/>
+      <c r="BQ16" s="2"/>
+      <c r="BR16" s="2"/>
+    </row>
+    <row r="17" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>43</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="BO17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
-      </c>
-      <c r="S18">
-        <v>1</v>
-      </c>
-      <c r="W18">
-        <v>1</v>
-      </c>
-      <c r="AC18">
-        <v>1</v>
-      </c>
-      <c r="BR18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="U19">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="V19">
         <v>1</v>
       </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="AD19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:73" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="Z21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="W22">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>1</v>
+      </c>
+      <c r="Y22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="X23">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>1</v>
-      </c>
-      <c r="Z23">
-        <v>1</v>
-      </c>
-      <c r="AB23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="2"/>
+      <c r="AM23" s="2"/>
+      <c r="AN23" s="2"/>
+      <c r="AO23" s="2"/>
+      <c r="AP23" s="2"/>
+      <c r="AQ23" s="2"/>
+      <c r="AR23" s="2"/>
+      <c r="AS23" s="2"/>
+      <c r="AT23" s="2"/>
+      <c r="AU23" s="2"/>
+      <c r="AV23" s="2"/>
+      <c r="AW23" s="2"/>
+      <c r="AX23" s="2"/>
+      <c r="AY23" s="2"/>
+      <c r="AZ23" s="2"/>
+      <c r="BA23" s="2"/>
+      <c r="BB23" s="2"/>
+      <c r="BC23" s="2"/>
+      <c r="BD23" s="2"/>
+      <c r="BE23" s="2"/>
+      <c r="BF23" s="2"/>
+      <c r="BG23" s="2"/>
+      <c r="BH23" s="2"/>
+      <c r="BI23" s="2"/>
+      <c r="BJ23" s="2"/>
+      <c r="BK23" s="2"/>
+      <c r="BL23" s="2"/>
+      <c r="BM23" s="2"/>
+      <c r="BN23" s="2"/>
+      <c r="BO23" s="2"/>
+      <c r="BP23" s="2"/>
+      <c r="BQ23" s="2"/>
+      <c r="BR23" s="2"/>
+    </row>
+    <row r="24" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2989,24 +2981,89 @@
       <c r="BP24" s="2"/>
       <c r="BQ24" s="2"/>
       <c r="BR24" s="2"/>
-      <c r="BS24" s="2"/>
-      <c r="BT24" s="2"/>
-      <c r="BU24" s="2"/>
-    </row>
-    <row r="25" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+      <c r="AO25" s="3"/>
+      <c r="AP25" s="3"/>
+      <c r="AQ25" s="3"/>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3"/>
+      <c r="AT25" s="3"/>
+      <c r="AU25" s="3"/>
+      <c r="AV25" s="3"/>
+      <c r="AW25" s="3"/>
+      <c r="AX25" s="3"/>
+      <c r="AY25" s="3"/>
+      <c r="AZ25" s="3"/>
+      <c r="BA25" s="3"/>
+      <c r="BB25" s="3"/>
+      <c r="BC25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BE25" s="3"/>
+      <c r="BF25" s="3"/>
+      <c r="BG25" s="3"/>
+      <c r="BH25" s="3"/>
+      <c r="BI25" s="3"/>
+      <c r="BJ25" s="3"/>
+      <c r="BK25" s="3"/>
+      <c r="BL25" s="3"/>
+      <c r="BM25" s="3"/>
+      <c r="BN25" s="3"/>
+      <c r="BO25" s="3"/>
+      <c r="BP25" s="3"/>
+      <c r="BQ25" s="3"/>
+      <c r="BR25" s="3"/>
+    </row>
+    <row r="26" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A26">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -3032,7 +3089,9 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
+      <c r="AA26" s="2">
+        <v>1</v>
+      </c>
       <c r="AB26" s="2"/>
       <c r="AC26" s="2"/>
       <c r="AD26" s="2"/>
@@ -3076,132 +3135,74 @@
       <c r="BP26" s="2"/>
       <c r="BQ26" s="2"/>
       <c r="BR26" s="2"/>
-      <c r="BS26" s="2"/>
-      <c r="BT26" s="2"/>
-      <c r="BU26" s="2"/>
-    </row>
-    <row r="27" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
-      <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="2"/>
-      <c r="AG27" s="2"/>
-      <c r="AH27" s="2"/>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
-      <c r="AK27" s="2"/>
-      <c r="AL27" s="2"/>
-      <c r="AM27" s="2"/>
-      <c r="AN27" s="2"/>
-      <c r="AO27" s="2"/>
-      <c r="AP27" s="2"/>
-      <c r="AQ27" s="2"/>
-      <c r="AR27" s="2"/>
-      <c r="AS27" s="2"/>
-      <c r="AT27" s="2"/>
-      <c r="AU27" s="2"/>
-      <c r="AV27" s="2"/>
-      <c r="AW27" s="2"/>
-      <c r="AX27" s="2"/>
-      <c r="AY27" s="2"/>
-      <c r="AZ27" s="2"/>
-      <c r="BA27" s="2"/>
-      <c r="BB27" s="2"/>
-      <c r="BC27" s="2"/>
-      <c r="BD27" s="2"/>
-      <c r="BE27" s="2"/>
-      <c r="BF27" s="2"/>
-      <c r="BG27" s="2"/>
-      <c r="BH27" s="2"/>
-      <c r="BI27" s="2"/>
-      <c r="BJ27" s="2"/>
-      <c r="BK27" s="2"/>
-      <c r="BL27" s="2"/>
-      <c r="BM27" s="2"/>
-      <c r="BN27" s="2"/>
-      <c r="BO27" s="2"/>
-      <c r="BP27" s="2"/>
-      <c r="BQ27" s="2"/>
-      <c r="BR27" s="2"/>
-      <c r="BS27" s="2"/>
-      <c r="BT27" s="2"/>
-      <c r="BU27" s="2"/>
-    </row>
-    <row r="28" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>1</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
+      <c r="M28" s="3">
+        <v>1</v>
+      </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
+      <c r="R28" s="3">
+        <v>1</v>
+      </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
+      <c r="U28" s="3">
+        <v>1</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
-      <c r="AA28" s="3">
-        <v>1</v>
-      </c>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
-      <c r="AC28" s="3"/>
+      <c r="AC28" s="3">
+        <v>1</v>
+      </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
       <c r="AH28" s="3"/>
-      <c r="AI28" s="3"/>
-      <c r="AJ28" s="3"/>
+      <c r="AI28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>1</v>
+      </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
@@ -3233,19 +3234,18 @@
       <c r="BM28" s="3"/>
       <c r="BN28" s="3"/>
       <c r="BO28" s="3"/>
-      <c r="BP28" s="3"/>
+      <c r="BP28" s="3">
+        <v>1</v>
+      </c>
       <c r="BQ28" s="3"/>
       <c r="BR28" s="3"/>
-      <c r="BS28" s="3"/>
-      <c r="BT28" s="3"/>
-      <c r="BU28" s="3"/>
-    </row>
-    <row r="29" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -3274,14 +3274,14 @@
       <c r="AA29" s="2"/>
       <c r="AB29" s="2"/>
       <c r="AC29" s="2"/>
-      <c r="AD29" s="2">
-        <v>1</v>
-      </c>
+      <c r="AD29" s="2"/>
       <c r="AE29" s="2"/>
       <c r="AF29" s="2"/>
       <c r="AG29" s="2"/>
       <c r="AH29" s="2"/>
-      <c r="AI29" s="2"/>
+      <c r="AI29" s="2">
+        <v>1</v>
+      </c>
       <c r="AJ29" s="2"/>
       <c r="AK29" s="2"/>
       <c r="AL29" s="2"/>
@@ -3317,870 +3317,860 @@
       <c r="BP29" s="2"/>
       <c r="BQ29" s="2"/>
       <c r="BR29" s="2"/>
-      <c r="BS29" s="2"/>
-      <c r="BT29" s="2"/>
-      <c r="BU29" s="2"/>
-    </row>
-    <row r="30" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30" s="2"/>
+      <c r="AK30" s="2"/>
+      <c r="AL30" s="2"/>
+      <c r="AM30" s="2"/>
+      <c r="AN30" s="2"/>
+      <c r="AO30" s="2"/>
+      <c r="AP30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ30" s="2"/>
+      <c r="AR30" s="2"/>
+      <c r="AS30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT30" s="2"/>
+      <c r="AU30" s="2"/>
+      <c r="AV30" s="2"/>
+      <c r="AW30" s="2"/>
+      <c r="AX30" s="2"/>
+      <c r="AY30" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ30" s="2"/>
+      <c r="BA30" s="2"/>
+      <c r="BB30" s="2"/>
+      <c r="BC30" s="2"/>
+      <c r="BD30" s="2"/>
+      <c r="BE30" s="2"/>
+      <c r="BF30" s="2"/>
+      <c r="BG30" s="2"/>
+      <c r="BH30" s="2"/>
+      <c r="BI30" s="2"/>
+      <c r="BJ30" s="2"/>
+      <c r="BK30" s="2"/>
+      <c r="BL30" s="2"/>
+      <c r="BM30" s="2"/>
+      <c r="BN30" s="2"/>
+      <c r="BO30" s="2"/>
+      <c r="BP30" s="2"/>
+      <c r="BQ30" s="2"/>
+      <c r="BR30" s="2"/>
+    </row>
+    <row r="31" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3">
-        <v>1</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1</v>
-      </c>
-      <c r="J31" s="3">
-        <v>1</v>
-      </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3">
-        <v>1</v>
-      </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3">
-        <v>1</v>
-      </c>
-      <c r="R31" s="3">
-        <v>1</v>
-      </c>
-      <c r="S31" s="3">
-        <v>1</v>
-      </c>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3">
-        <v>1</v>
-      </c>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-      <c r="AA31" s="3"/>
-      <c r="AB31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC31" s="3"/>
-      <c r="AD31" s="3"/>
-      <c r="AE31" s="3"/>
-      <c r="AF31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG31" s="3"/>
-      <c r="AH31" s="3"/>
-      <c r="AI31" s="3"/>
-      <c r="AJ31" s="3"/>
-      <c r="AK31" s="3"/>
-      <c r="AL31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM31" s="3">
-        <v>1</v>
-      </c>
-      <c r="AN31" s="3"/>
-      <c r="AO31" s="3"/>
-      <c r="AP31" s="3"/>
-      <c r="AQ31" s="3"/>
-      <c r="AR31" s="3"/>
-      <c r="AS31" s="3"/>
-      <c r="AT31" s="3"/>
-      <c r="AU31" s="3"/>
-      <c r="AV31" s="3"/>
-      <c r="AW31" s="3"/>
-      <c r="AX31" s="3"/>
-      <c r="AY31" s="3"/>
-      <c r="AZ31" s="3"/>
-      <c r="BA31" s="3"/>
-      <c r="BB31" s="3"/>
-      <c r="BC31" s="3"/>
-      <c r="BD31" s="3"/>
-      <c r="BE31" s="3"/>
-      <c r="BF31" s="3"/>
-      <c r="BG31" s="3"/>
-      <c r="BH31" s="3"/>
-      <c r="BI31" s="3"/>
-      <c r="BJ31" s="3"/>
-      <c r="BK31" s="3"/>
-      <c r="BL31" s="3"/>
-      <c r="BM31" s="3"/>
-      <c r="BN31" s="3"/>
-      <c r="BO31" s="3"/>
-      <c r="BP31" s="3"/>
-      <c r="BQ31" s="3"/>
-      <c r="BR31" s="3"/>
-      <c r="BS31" s="3">
-        <v>1</v>
-      </c>
-      <c r="BT31" s="3"/>
-      <c r="BU31" s="3"/>
-    </row>
-    <row r="32" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB31">
+        <v>1</v>
+      </c>
+      <c r="AC31">
+        <v>1</v>
+      </c>
+      <c r="AJ31">
+        <v>1</v>
+      </c>
+      <c r="AL31">
+        <v>1</v>
+      </c>
+      <c r="AM31">
+        <v>1</v>
+      </c>
+      <c r="AN31">
+        <v>1</v>
+      </c>
+      <c r="AO31">
+        <v>1</v>
+      </c>
+      <c r="AP31">
+        <v>1</v>
+      </c>
+      <c r="AQ31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB32">
+        <v>1</v>
+      </c>
+      <c r="AC32">
+        <v>1</v>
+      </c>
+      <c r="AJ32">
+        <v>1</v>
+      </c>
+      <c r="AQ32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A33">
         <v>34</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2">
-        <v>1</v>
-      </c>
-      <c r="R32" s="2">
-        <v>1</v>
-      </c>
-      <c r="S32" s="2">
-        <v>1</v>
-      </c>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
-      <c r="Z32" s="2"/>
-      <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="2"/>
-      <c r="AD32" s="2"/>
-      <c r="AE32" s="2"/>
-      <c r="AF32" s="2"/>
-      <c r="AG32" s="2"/>
-      <c r="AH32" s="2"/>
-      <c r="AI32" s="2"/>
-      <c r="AJ32" s="2"/>
-      <c r="AK32" s="2"/>
-      <c r="AL32" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM32" s="2"/>
-      <c r="AN32" s="2"/>
-      <c r="AO32" s="2"/>
-      <c r="AP32" s="2"/>
-      <c r="AQ32" s="2"/>
-      <c r="AR32" s="2"/>
-      <c r="AS32" s="2"/>
-      <c r="AT32" s="2"/>
-      <c r="AU32" s="2"/>
-      <c r="AV32" s="2"/>
-      <c r="AW32" s="2"/>
-      <c r="AX32" s="2"/>
-      <c r="AY32" s="2"/>
-      <c r="AZ32" s="2"/>
-      <c r="BA32" s="2"/>
-      <c r="BB32" s="2"/>
-      <c r="BC32" s="2"/>
-      <c r="BD32" s="2"/>
-      <c r="BE32" s="2"/>
-      <c r="BF32" s="2"/>
-      <c r="BG32" s="2"/>
-      <c r="BH32" s="2"/>
-      <c r="BI32" s="2"/>
-      <c r="BJ32" s="2"/>
-      <c r="BK32" s="2"/>
-      <c r="BL32" s="2"/>
-      <c r="BM32" s="2"/>
-      <c r="BN32" s="2"/>
-      <c r="BO32" s="2"/>
-      <c r="BP32" s="2"/>
-      <c r="BQ32" s="2"/>
-      <c r="BR32" s="2"/>
-      <c r="BS32" s="2"/>
-      <c r="BT32" s="2"/>
-      <c r="BU32" s="2"/>
-    </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
-      <c r="W33" s="2"/>
-      <c r="X33" s="2"/>
-      <c r="Y33" s="2"/>
-      <c r="Z33" s="2"/>
-      <c r="AA33" s="2"/>
-      <c r="AB33" s="2"/>
-      <c r="AC33" s="2"/>
-      <c r="AD33" s="2"/>
-      <c r="AE33" s="2"/>
-      <c r="AF33" s="2"/>
-      <c r="AG33" s="2"/>
-      <c r="AH33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI33" s="2"/>
-      <c r="AJ33" s="2"/>
-      <c r="AK33" s="2"/>
-      <c r="AL33" s="2"/>
-      <c r="AM33" s="2"/>
-      <c r="AN33" s="2"/>
-      <c r="AO33" s="2"/>
-      <c r="AP33" s="2"/>
-      <c r="AQ33" s="2"/>
-      <c r="AR33" s="2"/>
-      <c r="AS33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT33" s="2"/>
-      <c r="AU33" s="2"/>
-      <c r="AV33" s="2">
-        <v>1</v>
-      </c>
-      <c r="AW33" s="2"/>
-      <c r="AX33" s="2"/>
-      <c r="AY33" s="2"/>
-      <c r="AZ33" s="2"/>
-      <c r="BA33" s="2"/>
-      <c r="BB33" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC33" s="2"/>
-      <c r="BD33" s="2"/>
-      <c r="BE33" s="2"/>
-      <c r="BF33" s="2"/>
-      <c r="BG33" s="2"/>
-      <c r="BH33" s="2"/>
-      <c r="BI33" s="2"/>
-      <c r="BJ33" s="2"/>
-      <c r="BK33" s="2"/>
-      <c r="BL33" s="2"/>
-      <c r="BM33" s="2"/>
-      <c r="BN33" s="2"/>
-      <c r="BO33" s="2"/>
-      <c r="BP33" s="2"/>
-      <c r="BQ33" s="2"/>
-      <c r="BR33" s="2"/>
-      <c r="BS33" s="2"/>
-      <c r="BT33" s="2"/>
-      <c r="BU33" s="2"/>
-    </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC33">
+        <v>1</v>
+      </c>
+      <c r="AF33">
+        <v>1</v>
+      </c>
+      <c r="AS33">
+        <v>1</v>
+      </c>
+      <c r="AY33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A34">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AC34">
+        <v>1</v>
+      </c>
+      <c r="AF34">
+        <v>1</v>
+      </c>
+      <c r="AP34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A35">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <v>37</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
+      <c r="AG36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH36" s="2"/>
+      <c r="AI36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="2"/>
+      <c r="AK36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AP36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ36" s="2"/>
+      <c r="AR36" s="2"/>
+      <c r="AS36" s="2"/>
+      <c r="AT36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AU36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AX36" s="2"/>
+      <c r="AY36" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BA36" s="2"/>
+      <c r="BB36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BC36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BE36" s="2"/>
+      <c r="BF36" s="2"/>
+      <c r="BG36" s="2"/>
+      <c r="BH36" s="2"/>
+      <c r="BI36" s="2"/>
+      <c r="BJ36" s="2"/>
+      <c r="BK36" s="2"/>
+      <c r="BL36" s="2"/>
+      <c r="BM36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BN36" s="2"/>
+      <c r="BO36" s="2"/>
+      <c r="BP36" s="2">
+        <v>1</v>
+      </c>
+      <c r="BQ36" s="2"/>
+      <c r="BR36" s="2"/>
+    </row>
+    <row r="37" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE34">
-        <v>1</v>
-      </c>
-      <c r="AF34">
-        <v>1</v>
-      </c>
-      <c r="AM34">
-        <v>1</v>
-      </c>
-      <c r="AO34">
-        <v>1</v>
-      </c>
-      <c r="AP34">
-        <v>1</v>
-      </c>
-      <c r="AQ34">
-        <v>1</v>
-      </c>
-      <c r="AR34">
-        <v>1</v>
-      </c>
-      <c r="AS34">
-        <v>1</v>
-      </c>
-      <c r="AT34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="AC37">
+        <v>1</v>
+      </c>
+      <c r="AI37">
+        <v>1</v>
+      </c>
+      <c r="AV37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>5</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="AC38">
+        <v>1</v>
+      </c>
+      <c r="AM38">
+        <v>1</v>
+      </c>
+      <c r="AN38">
+        <v>1</v>
+      </c>
+      <c r="AO38">
+        <v>1</v>
+      </c>
+      <c r="AW38">
+        <v>1</v>
+      </c>
+      <c r="AY38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A39">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AP39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="3"/>
+      <c r="AT39" s="3"/>
+      <c r="AU39" s="3"/>
+      <c r="AV39" s="3"/>
+      <c r="AW39" s="3"/>
+      <c r="AX39" s="3"/>
+      <c r="AY39" s="3">
+        <v>1</v>
+      </c>
+      <c r="AZ39" s="3"/>
+      <c r="BA39" s="3"/>
+      <c r="BB39" s="3"/>
+      <c r="BC39" s="3"/>
+      <c r="BD39" s="3"/>
+      <c r="BE39" s="3"/>
+      <c r="BF39" s="3"/>
+      <c r="BG39" s="3"/>
+      <c r="BH39" s="3"/>
+      <c r="BI39" s="3"/>
+      <c r="BJ39" s="3"/>
+      <c r="BK39" s="3"/>
+      <c r="BL39" s="3"/>
+      <c r="BM39" s="3"/>
+      <c r="BN39" s="3"/>
+      <c r="BO39" s="3"/>
+      <c r="BP39" s="3"/>
+      <c r="BQ39" s="3"/>
+      <c r="BR39" s="3"/>
+    </row>
+    <row r="40" spans="1:70" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <v>41</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="AP40">
+        <v>1</v>
+      </c>
+      <c r="AY40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>6</v>
+      </c>
+      <c r="AP41">
+        <v>1</v>
+      </c>
+      <c r="AY41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A42">
+        <v>43</v>
+      </c>
+      <c r="B42" t="s">
+        <v>25</v>
+      </c>
+      <c r="AC42">
+        <v>1</v>
+      </c>
+      <c r="AI42">
+        <v>1</v>
+      </c>
+      <c r="AY42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A43">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5"/>
+      <c r="AA43" s="5"/>
+      <c r="AB43" s="5"/>
+      <c r="AC43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="5"/>
+      <c r="AF43" s="5"/>
+      <c r="AG43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AH43" s="5"/>
+      <c r="AI43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="5"/>
+      <c r="AK43" s="5"/>
+      <c r="AL43" s="5"/>
+      <c r="AM43" s="5"/>
+      <c r="AN43" s="5"/>
+      <c r="AO43" s="5"/>
+      <c r="AP43" s="5"/>
+      <c r="AQ43" s="5"/>
+      <c r="AR43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AT43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AU43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AV43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AW43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AX43" s="5"/>
+      <c r="AY43" s="5">
+        <v>1</v>
+      </c>
+      <c r="AZ43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BA43" s="5"/>
+      <c r="BB43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BC43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BD43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BE43" s="5"/>
+      <c r="BF43" s="5"/>
+      <c r="BG43" s="5"/>
+      <c r="BH43" s="5"/>
+      <c r="BI43" s="5"/>
+      <c r="BJ43" s="5"/>
+      <c r="BK43" s="5"/>
+      <c r="BL43" s="5"/>
+      <c r="BM43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BN43" s="5"/>
+      <c r="BO43" s="5">
+        <v>1</v>
+      </c>
+      <c r="BP43" s="5"/>
+      <c r="BQ43" s="5"/>
+      <c r="BR43" s="5"/>
+    </row>
+    <row r="44" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A44">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE35">
-        <v>1</v>
-      </c>
-      <c r="AF35">
-        <v>1</v>
-      </c>
-      <c r="AM35">
-        <v>1</v>
-      </c>
-      <c r="AT35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-      <c r="S36">
-        <v>1</v>
-      </c>
-      <c r="AF36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>1</v>
-      </c>
-      <c r="AV36">
-        <v>1</v>
-      </c>
-      <c r="BB36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
-        <v>80</v>
-      </c>
-      <c r="V37">
-        <v>1</v>
-      </c>
-      <c r="AF37">
-        <v>1</v>
-      </c>
-      <c r="AI37">
-        <v>1</v>
-      </c>
-      <c r="AS37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2">
-        <v>1</v>
-      </c>
-      <c r="R39" s="2">
-        <v>1</v>
-      </c>
-      <c r="S39" s="2">
-        <v>1</v>
-      </c>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2">
-        <v>1</v>
-      </c>
-      <c r="V39" s="2">
-        <v>1</v>
-      </c>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="2"/>
-      <c r="AA39" s="2"/>
-      <c r="AB39" s="2"/>
-      <c r="AC39" s="2"/>
-      <c r="AD39" s="2"/>
-      <c r="AE39" s="2"/>
-      <c r="AF39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH39" s="2"/>
-      <c r="AI39" s="2"/>
-      <c r="AJ39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK39" s="2"/>
-      <c r="AL39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM39" s="2"/>
-      <c r="AN39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AP39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AQ39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AR39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AS39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT39" s="2"/>
-      <c r="AU39" s="2"/>
-      <c r="AV39" s="2"/>
-      <c r="AW39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AX39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY39" s="2">
-        <v>1</v>
-      </c>
-      <c r="AZ39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BA39" s="2"/>
-      <c r="BB39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD39" s="2"/>
-      <c r="BE39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BG39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BH39" s="2"/>
-      <c r="BI39" s="2"/>
-      <c r="BJ39" s="2"/>
-      <c r="BK39" s="2"/>
-      <c r="BL39" s="2"/>
-      <c r="BM39" s="2"/>
-      <c r="BN39" s="2"/>
-      <c r="BO39" s="2"/>
-      <c r="BP39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ39" s="2"/>
-      <c r="BR39" s="2"/>
-      <c r="BS39" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT39" s="2"/>
-      <c r="BU39" s="2"/>
-    </row>
-    <row r="40" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF40">
-        <v>1</v>
-      </c>
-      <c r="AL40">
-        <v>1</v>
-      </c>
-      <c r="AY40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41">
-        <v>1</v>
-      </c>
-      <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="U41">
-        <v>1</v>
-      </c>
-      <c r="V41">
-        <v>1</v>
-      </c>
-      <c r="AF41">
-        <v>1</v>
-      </c>
-      <c r="AP41">
-        <v>1</v>
-      </c>
-      <c r="AQ41">
-        <v>1</v>
-      </c>
-      <c r="AR41">
-        <v>1</v>
-      </c>
-      <c r="AZ41">
-        <v>1</v>
-      </c>
-      <c r="BB41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3">
-        <v>1</v>
-      </c>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AG42" s="3"/>
-      <c r="AH42" s="3"/>
-      <c r="AI42" s="3"/>
-      <c r="AJ42" s="3"/>
-      <c r="AK42" s="3"/>
-      <c r="AL42" s="3"/>
-      <c r="AM42" s="3"/>
-      <c r="AN42" s="3"/>
-      <c r="AO42" s="3"/>
-      <c r="AP42" s="3"/>
-      <c r="AQ42" s="3"/>
-      <c r="AR42" s="3">
-        <v>1</v>
-      </c>
-      <c r="AS42" s="3">
-        <v>1</v>
-      </c>
-      <c r="AT42" s="3"/>
-      <c r="AU42" s="3"/>
-      <c r="AV42" s="3"/>
-      <c r="AW42" s="3"/>
-      <c r="AX42" s="3"/>
-      <c r="AY42" s="3"/>
-      <c r="AZ42" s="3"/>
-      <c r="BA42" s="3"/>
-      <c r="BB42" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC42" s="3"/>
-      <c r="BD42" s="3"/>
-      <c r="BE42" s="3"/>
-      <c r="BF42" s="3"/>
-      <c r="BG42" s="3"/>
-      <c r="BH42" s="3"/>
-      <c r="BI42" s="3"/>
-      <c r="BJ42" s="3"/>
-      <c r="BK42" s="3"/>
-      <c r="BL42" s="3"/>
-      <c r="BM42" s="3"/>
-      <c r="BN42" s="3"/>
-      <c r="BO42" s="3"/>
-      <c r="BP42" s="3"/>
-      <c r="BQ42" s="3"/>
-      <c r="BR42" s="3"/>
-      <c r="BS42" s="3"/>
-      <c r="BT42" s="3"/>
-      <c r="BU42" s="3"/>
-    </row>
-    <row r="43" spans="1:73" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="Q43">
-        <v>1</v>
-      </c>
-      <c r="S43">
-        <v>1</v>
-      </c>
-      <c r="AS43">
-        <v>1</v>
-      </c>
-      <c r="BB43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="S44">
-        <v>1</v>
-      </c>
-      <c r="AS44">
-        <v>1</v>
-      </c>
-      <c r="BB44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
+      <c r="AC44" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD44" s="3"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3"/>
+      <c r="AH44" s="3"/>
+      <c r="AI44" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ44" s="3"/>
+      <c r="AK44" s="3"/>
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="3"/>
+      <c r="AN44" s="3"/>
+      <c r="AO44" s="3"/>
+      <c r="AP44" s="3"/>
+      <c r="AQ44" s="3"/>
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="3"/>
+      <c r="AT44" s="3"/>
+      <c r="AU44" s="3"/>
+      <c r="AV44" s="3">
+        <v>1</v>
+      </c>
+      <c r="AW44" s="3"/>
+      <c r="AX44" s="3"/>
+      <c r="AY44" s="3"/>
+      <c r="AZ44" s="3"/>
+      <c r="BA44" s="3"/>
+      <c r="BB44" s="3"/>
+      <c r="BC44" s="3"/>
+      <c r="BD44" s="3"/>
+      <c r="BE44" s="3"/>
+      <c r="BF44" s="3"/>
+      <c r="BG44" s="3"/>
+      <c r="BH44" s="3"/>
+      <c r="BI44" s="3"/>
+      <c r="BJ44" s="3"/>
+      <c r="BK44" s="3"/>
+      <c r="BL44" s="3"/>
+      <c r="BM44" s="3"/>
+      <c r="BN44" s="3"/>
+      <c r="BO44" s="3"/>
+      <c r="BP44" s="3"/>
+      <c r="BQ44" s="3"/>
+      <c r="BR44" s="3"/>
+    </row>
+    <row r="45" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
-      </c>
-      <c r="V45">
-        <v>1</v>
-      </c>
-      <c r="AF45">
-        <v>1</v>
-      </c>
-      <c r="AL45">
-        <v>1</v>
-      </c>
-      <c r="BB45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="2"/>
+      <c r="AC45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD45" s="2"/>
+      <c r="AE45" s="2"/>
+      <c r="AF45" s="2"/>
+      <c r="AG45" s="2"/>
+      <c r="AH45" s="2"/>
+      <c r="AI45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ45" s="2"/>
+      <c r="AK45" s="2"/>
+      <c r="AL45" s="2"/>
+      <c r="AM45" s="2"/>
+      <c r="AN45" s="2"/>
+      <c r="AO45" s="2"/>
+      <c r="AP45" s="2"/>
+      <c r="AQ45" s="2"/>
+      <c r="AR45" s="2"/>
+      <c r="AS45" s="2"/>
+      <c r="AT45" s="2"/>
+      <c r="AU45" s="2"/>
+      <c r="AV45" s="2"/>
+      <c r="AW45" s="2"/>
+      <c r="AX45" s="2"/>
+      <c r="AY45" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ45" s="2"/>
+      <c r="BA45" s="2"/>
+      <c r="BB45" s="2"/>
+      <c r="BC45" s="2"/>
+      <c r="BD45" s="2"/>
+      <c r="BE45" s="2"/>
+      <c r="BF45" s="2"/>
+      <c r="BG45" s="2"/>
+      <c r="BH45" s="2"/>
+      <c r="BI45" s="2"/>
+      <c r="BJ45" s="2"/>
+      <c r="BK45" s="2"/>
+      <c r="BL45" s="2"/>
+      <c r="BM45" s="2"/>
+      <c r="BN45" s="2"/>
+      <c r="BO45" s="2"/>
+      <c r="BP45" s="2"/>
+      <c r="BQ45" s="2"/>
+      <c r="BR45" s="2"/>
+    </row>
+    <row r="46" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5">
-        <v>1</v>
-      </c>
-      <c r="R46" s="5">
-        <v>1</v>
-      </c>
-      <c r="S46" s="5">
-        <v>1</v>
-      </c>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
-      <c r="V46" s="5">
-        <v>1</v>
-      </c>
-      <c r="W46" s="5"/>
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5"/>
-      <c r="Z46" s="5"/>
-      <c r="AA46" s="5"/>
-      <c r="AB46" s="5"/>
-      <c r="AC46" s="5"/>
-      <c r="AD46" s="5"/>
-      <c r="AE46" s="5"/>
-      <c r="AF46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AG46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AH46" s="5"/>
-      <c r="AI46" s="5"/>
-      <c r="AJ46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AK46" s="5"/>
-      <c r="AL46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AM46" s="5"/>
-      <c r="AN46" s="5"/>
-      <c r="AO46" s="5"/>
-      <c r="AP46" s="5"/>
-      <c r="AQ46" s="5"/>
-      <c r="AR46" s="5"/>
-      <c r="AS46" s="5"/>
-      <c r="AT46" s="5"/>
-      <c r="AU46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AV46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AW46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AX46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AY46" s="5">
-        <v>1</v>
-      </c>
-      <c r="AZ46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BA46" s="5"/>
-      <c r="BB46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BC46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BD46" s="5"/>
-      <c r="BE46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BF46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BG46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BH46" s="5"/>
-      <c r="BI46" s="5"/>
-      <c r="BJ46" s="5"/>
-      <c r="BK46" s="5"/>
-      <c r="BL46" s="5"/>
-      <c r="BM46" s="5"/>
-      <c r="BN46" s="5"/>
-      <c r="BO46" s="5"/>
-      <c r="BP46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BQ46" s="5"/>
-      <c r="BR46" s="5">
-        <v>1</v>
-      </c>
-      <c r="BS46" s="5"/>
-      <c r="BT46" s="5"/>
-      <c r="BU46" s="5"/>
-    </row>
-    <row r="47" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="2">
+        <v>1</v>
+      </c>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD46" s="2"/>
+      <c r="AE46" s="2"/>
+      <c r="AF46" s="2"/>
+      <c r="AG46" s="2"/>
+      <c r="AH46" s="2"/>
+      <c r="AI46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ46" s="2"/>
+      <c r="AK46" s="2"/>
+      <c r="AL46" s="2"/>
+      <c r="AM46" s="2"/>
+      <c r="AN46" s="2"/>
+      <c r="AO46" s="2"/>
+      <c r="AP46" s="2"/>
+      <c r="AQ46" s="2"/>
+      <c r="AR46" s="2"/>
+      <c r="AS46" s="2"/>
+      <c r="AT46" s="2"/>
+      <c r="AU46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AV46" s="2"/>
+      <c r="AW46" s="2"/>
+      <c r="AX46" s="2"/>
+      <c r="AY46" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ46" s="2"/>
+      <c r="BA46" s="2"/>
+      <c r="BB46" s="2"/>
+      <c r="BC46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BE46" s="2"/>
+      <c r="BF46" s="2"/>
+      <c r="BG46" s="2"/>
+      <c r="BH46" s="2"/>
+      <c r="BI46" s="2"/>
+      <c r="BJ46" s="2"/>
+      <c r="BK46" s="2"/>
+      <c r="BL46" s="2"/>
+      <c r="BM46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BN46" s="2"/>
+      <c r="BO46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BQ46" s="2"/>
+      <c r="BR46" s="2"/>
+    </row>
+    <row r="47" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -4211,17 +4201,13 @@
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3"/>
-      <c r="AF47" s="3">
-        <v>1</v>
-      </c>
+      <c r="AF47" s="3"/>
       <c r="AG47" s="3"/>
       <c r="AH47" s="3"/>
       <c r="AI47" s="3"/>
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
-      <c r="AL47" s="3">
-        <v>1</v>
-      </c>
+      <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
       <c r="AN47" s="3"/>
       <c r="AO47" s="3"/>
@@ -4234,9 +4220,7 @@
       <c r="AV47" s="3"/>
       <c r="AW47" s="3"/>
       <c r="AX47" s="3"/>
-      <c r="AY47" s="3">
-        <v>1</v>
-      </c>
+      <c r="AY47" s="3"/>
       <c r="AZ47" s="3"/>
       <c r="BA47" s="3"/>
       <c r="BB47" s="3"/>
@@ -4256,16 +4240,13 @@
       <c r="BP47" s="3"/>
       <c r="BQ47" s="3"/>
       <c r="BR47" s="3"/>
-      <c r="BS47" s="3"/>
-      <c r="BT47" s="3"/>
-      <c r="BU47" s="3"/>
-    </row>
-    <row r="48" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A48">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -4284,31 +4265,31 @@
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
-      <c r="T48" s="2"/>
+      <c r="T48" s="2">
+        <v>1</v>
+      </c>
       <c r="U48" s="2"/>
-      <c r="V48" s="2">
-        <v>1</v>
-      </c>
+      <c r="V48" s="2"/>
       <c r="W48" s="2"/>
       <c r="X48" s="2"/>
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
       <c r="AB48" s="2"/>
-      <c r="AC48" s="2"/>
+      <c r="AC48" s="2">
+        <v>1</v>
+      </c>
       <c r="AD48" s="2"/>
       <c r="AE48" s="2"/>
-      <c r="AF48" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF48" s="2"/>
       <c r="AG48" s="2"/>
       <c r="AH48" s="2"/>
-      <c r="AI48" s="2"/>
+      <c r="AI48" s="2">
+        <v>1</v>
+      </c>
       <c r="AJ48" s="2"/>
       <c r="AK48" s="2"/>
-      <c r="AL48" s="2">
-        <v>1</v>
-      </c>
+      <c r="AL48" s="2"/>
       <c r="AM48" s="2"/>
       <c r="AN48" s="2"/>
       <c r="AO48" s="2"/>
@@ -4319,16 +4300,24 @@
       <c r="AT48" s="2"/>
       <c r="AU48" s="2"/>
       <c r="AV48" s="2"/>
-      <c r="AW48" s="2"/>
-      <c r="AX48" s="2"/>
-      <c r="AY48" s="2"/>
+      <c r="AW48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AX48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AY48" s="2">
+        <v>1</v>
+      </c>
       <c r="AZ48" s="2"/>
       <c r="BA48" s="2"/>
-      <c r="BB48" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC48" s="2"/>
-      <c r="BD48" s="2"/>
+      <c r="BB48" s="2"/>
+      <c r="BC48" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD48" s="2">
+        <v>1</v>
+      </c>
       <c r="BE48" s="2"/>
       <c r="BF48" s="2"/>
       <c r="BG48" s="2"/>
@@ -4337,439 +4326,282 @@
       <c r="BJ48" s="2"/>
       <c r="BK48" s="2"/>
       <c r="BL48" s="2"/>
-      <c r="BM48" s="2"/>
+      <c r="BM48" s="2">
+        <v>1</v>
+      </c>
       <c r="BN48" s="2"/>
-      <c r="BO48" s="2"/>
-      <c r="BP48" s="2"/>
+      <c r="BO48" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP48" s="2">
+        <v>1</v>
+      </c>
       <c r="BQ48" s="2"/>
       <c r="BR48" s="2"/>
-      <c r="BS48" s="2"/>
-      <c r="BT48" s="2"/>
-      <c r="BU48" s="2"/>
-    </row>
-    <row r="49" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2">
-        <v>1</v>
-      </c>
-      <c r="R49" s="2">
-        <v>1</v>
-      </c>
-      <c r="S49" s="2">
-        <v>1</v>
-      </c>
-      <c r="T49" s="2"/>
-      <c r="U49" s="2">
-        <v>1</v>
-      </c>
-      <c r="V49" s="2">
-        <v>1</v>
-      </c>
-      <c r="W49" s="2"/>
-      <c r="X49" s="2"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2"/>
-      <c r="AB49" s="2"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="2"/>
-      <c r="AE49" s="2"/>
-      <c r="AF49" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG49" s="2"/>
-      <c r="AH49" s="2"/>
-      <c r="AI49" s="2"/>
-      <c r="AJ49" s="2"/>
-      <c r="AK49" s="2"/>
-      <c r="AL49" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM49" s="2"/>
-      <c r="AN49" s="2"/>
-      <c r="AO49" s="2"/>
-      <c r="AP49" s="2"/>
-      <c r="AQ49" s="2"/>
-      <c r="AR49" s="2"/>
-      <c r="AS49" s="2"/>
-      <c r="AT49" s="2"/>
-      <c r="AU49" s="2"/>
-      <c r="AV49" s="2"/>
-      <c r="AW49" s="2"/>
-      <c r="AX49" s="2">
-        <v>1</v>
-      </c>
-      <c r="AY49" s="2"/>
-      <c r="AZ49" s="2"/>
-      <c r="BA49" s="2"/>
-      <c r="BB49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC49" s="2"/>
-      <c r="BD49" s="2"/>
-      <c r="BE49" s="2"/>
-      <c r="BF49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BG49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BH49" s="2"/>
-      <c r="BI49" s="2"/>
-      <c r="BJ49" s="2"/>
-      <c r="BK49" s="2"/>
-      <c r="BL49" s="2"/>
-      <c r="BM49" s="2"/>
-      <c r="BN49" s="2"/>
-      <c r="BO49" s="2"/>
-      <c r="BP49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ49" s="2"/>
-      <c r="BR49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS49" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT49" s="2"/>
-      <c r="BU49" s="2"/>
-    </row>
-    <row r="50" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC49">
+        <v>1</v>
+      </c>
+      <c r="AY49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
-      <c r="AB50" s="3"/>
-      <c r="AC50" s="3"/>
-      <c r="AD50" s="3"/>
-      <c r="AE50" s="3"/>
-      <c r="AF50" s="3"/>
-      <c r="AG50" s="3"/>
-      <c r="AH50" s="3"/>
-      <c r="AI50" s="3"/>
-      <c r="AJ50" s="3"/>
-      <c r="AK50" s="3"/>
-      <c r="AL50" s="3"/>
-      <c r="AM50" s="3"/>
-      <c r="AN50" s="3"/>
-      <c r="AO50" s="3"/>
-      <c r="AP50" s="3"/>
-      <c r="AQ50" s="3"/>
-      <c r="AR50" s="3"/>
-      <c r="AS50" s="3"/>
-      <c r="AT50" s="3"/>
-      <c r="AU50" s="3"/>
-      <c r="AV50" s="3"/>
-      <c r="AW50" s="3"/>
-      <c r="AX50" s="3"/>
-      <c r="AY50" s="3"/>
-      <c r="AZ50" s="3"/>
-      <c r="BA50" s="3"/>
-      <c r="BB50" s="3"/>
-      <c r="BC50" s="3"/>
-      <c r="BD50" s="3"/>
-      <c r="BE50" s="3"/>
-      <c r="BF50" s="3"/>
-      <c r="BG50" s="3"/>
-      <c r="BH50" s="3"/>
-      <c r="BI50" s="3"/>
-      <c r="BJ50" s="3"/>
-      <c r="BK50" s="3"/>
-      <c r="BL50" s="3"/>
-      <c r="BM50" s="3"/>
-      <c r="BN50" s="3"/>
-      <c r="BO50" s="3"/>
-      <c r="BP50" s="3"/>
-      <c r="BQ50" s="3"/>
-      <c r="BR50" s="3"/>
-      <c r="BS50" s="3"/>
-      <c r="BT50" s="3"/>
-      <c r="BU50" s="3"/>
-    </row>
-    <row r="51" spans="1:73" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="B50" t="s">
+        <v>70</v>
+      </c>
+      <c r="AC50">
+        <v>1</v>
+      </c>
+      <c r="AI50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2">
-        <v>1</v>
-      </c>
-      <c r="R51" s="2">
-        <v>1</v>
-      </c>
-      <c r="S51" s="2">
-        <v>1</v>
-      </c>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2">
-        <v>1</v>
-      </c>
-      <c r="V51" s="2">
-        <v>1</v>
-      </c>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="2"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="2"/>
-      <c r="AE51" s="2"/>
-      <c r="AF51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG51" s="2"/>
-      <c r="AH51" s="2"/>
-      <c r="AI51" s="2"/>
-      <c r="AJ51" s="2"/>
-      <c r="AK51" s="2"/>
-      <c r="AL51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM51" s="2"/>
-      <c r="AN51" s="2"/>
-      <c r="AO51" s="2"/>
-      <c r="AP51" s="2"/>
-      <c r="AQ51" s="2"/>
-      <c r="AR51" s="2"/>
-      <c r="AS51" s="2"/>
-      <c r="AT51" s="2"/>
-      <c r="AU51" s="2"/>
-      <c r="AV51" s="2"/>
-      <c r="AW51" s="2"/>
-      <c r="AX51" s="2"/>
-      <c r="AY51" s="2"/>
-      <c r="AZ51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BA51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BB51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BC51" s="2"/>
-      <c r="BD51" s="2"/>
-      <c r="BE51" s="2"/>
-      <c r="BF51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BG51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BH51" s="2"/>
-      <c r="BI51" s="2"/>
-      <c r="BJ51" s="2"/>
-      <c r="BK51" s="2"/>
-      <c r="BL51" s="2"/>
-      <c r="BM51" s="2"/>
-      <c r="BN51" s="2"/>
-      <c r="BO51" s="2"/>
-      <c r="BP51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BQ51" s="2"/>
-      <c r="BR51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BS51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BT51" s="2"/>
-      <c r="BU51" s="2"/>
-    </row>
-    <row r="52" spans="1:73" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3"/>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3"/>
+      <c r="AC51" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+      <c r="AH51" s="3"/>
+      <c r="AI51" s="3">
+        <v>1</v>
+      </c>
+      <c r="AJ51" s="3"/>
+      <c r="AK51" s="3"/>
+      <c r="AL51" s="3"/>
+      <c r="AM51" s="3"/>
+      <c r="AN51" s="3"/>
+      <c r="AO51" s="3"/>
+      <c r="AP51" s="3"/>
+      <c r="AQ51" s="3"/>
+      <c r="AR51" s="3"/>
+      <c r="AS51" s="3"/>
+      <c r="AT51" s="3"/>
+      <c r="AU51" s="3"/>
+      <c r="AV51" s="3"/>
+      <c r="AW51" s="3"/>
+      <c r="AX51" s="3"/>
+      <c r="AY51" s="3"/>
+      <c r="AZ51" s="3"/>
+      <c r="BA51" s="3"/>
+      <c r="BB51" s="3"/>
+      <c r="BC51" s="3"/>
+      <c r="BD51" s="3"/>
+      <c r="BE51" s="3"/>
+      <c r="BF51" s="3"/>
+      <c r="BG51" s="3"/>
+      <c r="BH51" s="3"/>
+      <c r="BI51" s="3"/>
+      <c r="BJ51" s="3"/>
+      <c r="BK51" s="3"/>
+      <c r="BL51" s="3"/>
+      <c r="BM51" s="3"/>
+      <c r="BN51" s="3"/>
+      <c r="BO51" s="3"/>
+      <c r="BP51" s="3"/>
+      <c r="BQ51" s="3"/>
+      <c r="BR51" s="3"/>
+    </row>
+    <row r="52" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q52">
-        <v>1</v>
-      </c>
-      <c r="S52">
-        <v>1</v>
-      </c>
-      <c r="V52">
-        <v>1</v>
-      </c>
-      <c r="AF52">
-        <v>1</v>
-      </c>
-      <c r="BB52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:73" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2">
+        <v>1</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>1</v>
+      </c>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+      <c r="AA52" s="2"/>
+      <c r="AB52" s="2"/>
+      <c r="AC52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD52" s="2"/>
+      <c r="AE52" s="2"/>
+      <c r="AF52" s="2"/>
+      <c r="AG52" s="2"/>
+      <c r="AH52" s="2"/>
+      <c r="AI52" s="2"/>
+      <c r="AJ52" s="2"/>
+      <c r="AK52" s="2"/>
+      <c r="AL52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM52" s="2"/>
+      <c r="AN52" s="2"/>
+      <c r="AO52" s="2"/>
+      <c r="AP52" s="2"/>
+      <c r="AQ52" s="2"/>
+      <c r="AR52" s="2"/>
+      <c r="AS52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT52" s="2"/>
+      <c r="AU52" s="2"/>
+      <c r="AV52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AW52" s="2"/>
+      <c r="AX52" s="2"/>
+      <c r="AY52" s="2">
+        <v>1</v>
+      </c>
+      <c r="AZ52" s="2"/>
+      <c r="BA52" s="2">
+        <v>1</v>
+      </c>
+      <c r="BB52" s="2"/>
+      <c r="BC52" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD52" s="2">
+        <v>1</v>
+      </c>
+      <c r="BE52" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF52" s="2"/>
+      <c r="BG52" s="2"/>
+      <c r="BH52" s="2"/>
+      <c r="BI52" s="2"/>
+      <c r="BJ52" s="2"/>
+      <c r="BK52" s="2"/>
+      <c r="BL52" s="2"/>
+      <c r="BM52" s="2"/>
+      <c r="BN52" s="2"/>
+      <c r="BO52" s="2"/>
+      <c r="BP52" s="2"/>
+      <c r="BQ52" s="2"/>
+      <c r="BR52" s="2"/>
+    </row>
+    <row r="53" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A53">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF53">
-        <v>1</v>
-      </c>
-      <c r="AL53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+      <c r="Z53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3">
-        <v>1</v>
-      </c>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
-      <c r="AB54" s="3"/>
-      <c r="AC54" s="3"/>
-      <c r="AD54" s="3"/>
-      <c r="AE54" s="3"/>
-      <c r="AF54" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG54" s="3"/>
-      <c r="AH54" s="3"/>
-      <c r="AI54" s="3"/>
-      <c r="AJ54" s="3"/>
-      <c r="AK54" s="3"/>
-      <c r="AL54" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM54" s="3"/>
-      <c r="AN54" s="3"/>
-      <c r="AO54" s="3"/>
-      <c r="AP54" s="3"/>
-      <c r="AQ54" s="3"/>
-      <c r="AR54" s="3"/>
-      <c r="AS54" s="3"/>
-      <c r="AT54" s="3"/>
-      <c r="AU54" s="3"/>
-      <c r="AV54" s="3"/>
-      <c r="AW54" s="3"/>
-      <c r="AX54" s="3"/>
-      <c r="AY54" s="3"/>
-      <c r="AZ54" s="3"/>
-      <c r="BA54" s="3"/>
-      <c r="BB54" s="3"/>
-      <c r="BC54" s="3"/>
-      <c r="BD54" s="3"/>
-      <c r="BE54" s="3"/>
-      <c r="BF54" s="3"/>
-      <c r="BG54" s="3"/>
-      <c r="BH54" s="3"/>
-      <c r="BI54" s="3"/>
-      <c r="BJ54" s="3"/>
-      <c r="BK54" s="3"/>
-      <c r="BL54" s="3"/>
-      <c r="BM54" s="3"/>
-      <c r="BN54" s="3"/>
-      <c r="BO54" s="3"/>
-      <c r="BP54" s="3"/>
-      <c r="BQ54" s="3"/>
-      <c r="BR54" s="3"/>
-      <c r="BS54" s="3"/>
-      <c r="BT54" s="3"/>
-      <c r="BU54" s="3"/>
-    </row>
-    <row r="55" spans="1:73" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC54">
+        <v>1</v>
+      </c>
+      <c r="AJ54">
+        <v>1</v>
+      </c>
+      <c r="AS54">
+        <v>1</v>
+      </c>
+      <c r="AV54">
+        <v>1</v>
+      </c>
+      <c r="AY54">
+        <v>1</v>
+      </c>
+      <c r="AZ54">
+        <v>1</v>
+      </c>
+      <c r="BA54">
+        <v>1</v>
+      </c>
+      <c r="BC54">
+        <v>1</v>
+      </c>
+      <c r="BD54">
+        <v>1</v>
+      </c>
+      <c r="BE54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -4784,15 +4616,9 @@
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
-      <c r="P55" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q55" s="2">
-        <v>1</v>
-      </c>
-      <c r="R55" s="2">
-        <v>1</v>
-      </c>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
@@ -4806,9 +4632,7 @@
       <c r="AC55" s="2"/>
       <c r="AD55" s="2"/>
       <c r="AE55" s="2"/>
-      <c r="AF55" s="2">
-        <v>1</v>
-      </c>
+      <c r="AF55" s="2"/>
       <c r="AG55" s="2"/>
       <c r="AH55" s="2"/>
       <c r="AI55" s="2"/>
@@ -4817,42 +4641,26 @@
       <c r="AL55" s="2"/>
       <c r="AM55" s="2"/>
       <c r="AN55" s="2"/>
-      <c r="AO55" s="2">
-        <v>1</v>
-      </c>
+      <c r="AO55" s="2"/>
       <c r="AP55" s="2"/>
       <c r="AQ55" s="2"/>
       <c r="AR55" s="2"/>
       <c r="AS55" s="2"/>
       <c r="AT55" s="2"/>
       <c r="AU55" s="2"/>
-      <c r="AV55" s="2">
-        <v>1</v>
-      </c>
+      <c r="AV55" s="2"/>
       <c r="AW55" s="2"/>
       <c r="AX55" s="2"/>
-      <c r="AY55" s="2">
-        <v>1</v>
-      </c>
+      <c r="AY55" s="2"/>
       <c r="AZ55" s="2"/>
       <c r="BA55" s="2"/>
-      <c r="BB55" s="2">
-        <v>1</v>
-      </c>
+      <c r="BB55" s="2"/>
       <c r="BC55" s="2"/>
-      <c r="BD55" s="2">
-        <v>1</v>
-      </c>
+      <c r="BD55" s="2"/>
       <c r="BE55" s="2"/>
-      <c r="BF55" s="2">
-        <v>1</v>
-      </c>
-      <c r="BG55" s="2">
-        <v>1</v>
-      </c>
-      <c r="BH55" s="2">
-        <v>1</v>
-      </c>
+      <c r="BF55" s="2"/>
+      <c r="BG55" s="2"/>
+      <c r="BH55" s="2"/>
       <c r="BI55" s="2"/>
       <c r="BJ55" s="2"/>
       <c r="BK55" s="2"/>
@@ -4863,407 +4671,365 @@
       <c r="BP55" s="2"/>
       <c r="BQ55" s="2"/>
       <c r="BR55" s="2"/>
-      <c r="BS55" s="2"/>
-      <c r="BT55" s="2"/>
-      <c r="BU55" s="2"/>
-    </row>
-    <row r="56" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A56">
-        <v>54</v>
-      </c>
-      <c r="B56" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56">
-        <v>1</v>
-      </c>
-      <c r="AC56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
+      <c r="AA56" s="2"/>
+      <c r="AB56" s="2"/>
+      <c r="AC56" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="2"/>
+      <c r="AE56" s="2"/>
+      <c r="AF56" s="2"/>
+      <c r="AG56" s="2"/>
+      <c r="AH56" s="2"/>
+      <c r="AI56" s="2"/>
+      <c r="AJ56" s="2"/>
+      <c r="AK56" s="2"/>
+      <c r="AL56" s="2"/>
+      <c r="AM56" s="2"/>
+      <c r="AN56" s="2"/>
+      <c r="AO56" s="2"/>
+      <c r="AP56" s="2"/>
+      <c r="AQ56" s="2"/>
+      <c r="AR56" s="2"/>
+      <c r="AS56" s="2"/>
+      <c r="AT56" s="2"/>
+      <c r="AU56" s="2"/>
+      <c r="AV56" s="2"/>
+      <c r="AW56" s="2"/>
+      <c r="AX56" s="2"/>
+      <c r="AY56" s="2"/>
+      <c r="AZ56" s="2"/>
+      <c r="BA56" s="2"/>
+      <c r="BB56" s="2"/>
+      <c r="BC56" s="2"/>
+      <c r="BD56" s="2"/>
+      <c r="BE56" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF56" s="2">
+        <v>1</v>
+      </c>
+      <c r="BG56" s="2"/>
+      <c r="BH56" s="2"/>
+      <c r="BI56" s="2"/>
+      <c r="BJ56" s="2"/>
+      <c r="BK56" s="2"/>
+      <c r="BL56" s="2"/>
+      <c r="BM56" s="2"/>
+      <c r="BN56" s="2"/>
+      <c r="BO56" s="2"/>
+      <c r="BP56" s="2"/>
+      <c r="BQ56" s="2"/>
+      <c r="BR56" s="2"/>
+    </row>
+    <row r="57" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57">
+        <v>58</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+      <c r="AH57" s="3"/>
+      <c r="AI57" s="3"/>
+      <c r="AJ57" s="3"/>
+      <c r="AK57" s="3"/>
+      <c r="AL57" s="3"/>
+      <c r="AM57" s="3"/>
+      <c r="AN57" s="3"/>
+      <c r="AO57" s="3"/>
+      <c r="AP57" s="3"/>
+      <c r="AQ57" s="3"/>
+      <c r="AR57" s="3"/>
+      <c r="AS57" s="3"/>
+      <c r="AT57" s="3"/>
+      <c r="AU57" s="3"/>
+      <c r="AV57" s="3"/>
+      <c r="AW57" s="3"/>
+      <c r="AX57" s="3"/>
+      <c r="AY57" s="3"/>
+      <c r="AZ57" s="3"/>
+      <c r="BA57" s="3"/>
+      <c r="BB57" s="3"/>
+      <c r="BC57" s="3"/>
+      <c r="BD57" s="3"/>
+      <c r="BE57" s="3"/>
+      <c r="BF57" s="3">
+        <v>1</v>
+      </c>
+      <c r="BG57" s="3"/>
+      <c r="BH57" s="3"/>
+      <c r="BI57" s="3"/>
+      <c r="BJ57" s="3"/>
+      <c r="BK57" s="3"/>
+      <c r="BL57" s="3"/>
+      <c r="BM57" s="3"/>
+      <c r="BN57" s="3"/>
+      <c r="BO57" s="3"/>
+      <c r="BP57" s="3"/>
+      <c r="BQ57" s="3"/>
+      <c r="BR57" s="3"/>
+    </row>
+    <row r="58" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <v>59</v>
+      </c>
+      <c r="B58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A59">
+        <v>60</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+      <c r="K59" s="3"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3">
+        <v>1</v>
+      </c>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="3"/>
+      <c r="R59" s="3"/>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="3"/>
+      <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
+      <c r="X59" s="3"/>
+      <c r="Y59" s="3"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+      <c r="AH59" s="3"/>
+      <c r="AI59" s="3"/>
+      <c r="AJ59" s="3"/>
+      <c r="AK59" s="3"/>
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3"/>
+      <c r="AN59" s="3"/>
+      <c r="AO59" s="3"/>
+      <c r="AP59" s="3"/>
+      <c r="AQ59" s="3"/>
+      <c r="AR59" s="3"/>
+      <c r="AS59" s="3"/>
+      <c r="AT59" s="3"/>
+      <c r="AU59" s="3"/>
+      <c r="AV59" s="3"/>
+      <c r="AW59" s="3"/>
+      <c r="AX59" s="3"/>
+      <c r="AY59" s="3"/>
+      <c r="AZ59" s="3"/>
+      <c r="BA59" s="3"/>
+      <c r="BB59" s="3"/>
+      <c r="BC59" s="3"/>
+      <c r="BD59" s="3"/>
+      <c r="BE59" s="3"/>
+      <c r="BF59" s="3"/>
+      <c r="BG59" s="3"/>
+      <c r="BH59" s="3"/>
+      <c r="BI59" s="3"/>
+      <c r="BJ59" s="3"/>
+      <c r="BK59" s="3"/>
+      <c r="BL59" s="3"/>
+      <c r="BM59" s="3"/>
+      <c r="BN59" s="3"/>
+      <c r="BO59" s="3"/>
+      <c r="BP59" s="3"/>
+      <c r="BQ59" s="3"/>
+      <c r="BR59" s="3"/>
+    </row>
+    <row r="60" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <v>61</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
+      <c r="AA60" s="2"/>
+      <c r="AB60" s="2"/>
+      <c r="AC60" s="2"/>
+      <c r="AD60" s="2"/>
+      <c r="AE60" s="2"/>
+      <c r="AF60" s="2"/>
+      <c r="AG60" s="2"/>
+      <c r="AH60" s="2"/>
+      <c r="AI60" s="2"/>
+      <c r="AJ60" s="2"/>
+      <c r="AK60" s="2"/>
+      <c r="AL60" s="2"/>
+      <c r="AM60" s="2"/>
+      <c r="AN60" s="2"/>
+      <c r="AO60" s="2"/>
+      <c r="AP60" s="2"/>
+      <c r="AQ60" s="2"/>
+      <c r="AR60" s="2"/>
+      <c r="AS60" s="2"/>
+      <c r="AT60" s="2"/>
+      <c r="AU60" s="2"/>
+      <c r="AV60" s="2"/>
+      <c r="AW60" s="2"/>
+      <c r="AX60" s="2"/>
+      <c r="AY60" s="2"/>
+      <c r="AZ60" s="2"/>
+      <c r="BA60" s="2"/>
+      <c r="BB60" s="2"/>
+      <c r="BC60" s="2"/>
+      <c r="BD60" s="2"/>
+      <c r="BE60" s="2"/>
+      <c r="BF60" s="2"/>
+      <c r="BG60" s="2">
+        <v>1</v>
+      </c>
+      <c r="BH60" s="2"/>
+      <c r="BI60" s="2"/>
+      <c r="BJ60" s="2"/>
+      <c r="BK60" s="2"/>
+      <c r="BL60" s="2"/>
+      <c r="BM60" s="2"/>
+      <c r="BN60" s="2"/>
+      <c r="BO60" s="2"/>
+      <c r="BP60" s="2"/>
+      <c r="BQ60" s="2"/>
+      <c r="BR60" s="2"/>
+    </row>
+    <row r="61" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <v>62</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="BJ61">
+        <v>1</v>
+      </c>
+      <c r="BK61">
+        <v>1</v>
+      </c>
+      <c r="BL61">
+        <v>1</v>
+      </c>
+      <c r="BM61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A62">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <v>64</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q57">
-        <v>1</v>
-      </c>
-      <c r="AF57">
-        <v>1</v>
-      </c>
-      <c r="AM57">
-        <v>1</v>
-      </c>
-      <c r="AV57">
-        <v>1</v>
-      </c>
-      <c r="AY57">
-        <v>1</v>
-      </c>
-      <c r="BB57">
-        <v>1</v>
-      </c>
-      <c r="BC57">
-        <v>1</v>
-      </c>
-      <c r="BD57">
-        <v>1</v>
-      </c>
-      <c r="BF57">
-        <v>1</v>
-      </c>
-      <c r="BG57">
-        <v>1</v>
-      </c>
-      <c r="BH57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>56</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="2"/>
-      <c r="AA58" s="2"/>
-      <c r="AB58" s="2"/>
-      <c r="AC58" s="2"/>
-      <c r="AD58" s="2"/>
-      <c r="AE58" s="2"/>
-      <c r="AF58" s="2"/>
-      <c r="AG58" s="2"/>
-      <c r="AH58" s="2"/>
-      <c r="AI58" s="2"/>
-      <c r="AJ58" s="2"/>
-      <c r="AK58" s="2"/>
-      <c r="AL58" s="2"/>
-      <c r="AM58" s="2"/>
-      <c r="AN58" s="2"/>
-      <c r="AO58" s="2"/>
-      <c r="AP58" s="2"/>
-      <c r="AQ58" s="2"/>
-      <c r="AR58" s="2"/>
-      <c r="AS58" s="2"/>
-      <c r="AT58" s="2"/>
-      <c r="AU58" s="2"/>
-      <c r="AV58" s="2"/>
-      <c r="AW58" s="2"/>
-      <c r="AX58" s="2"/>
-      <c r="AY58" s="2"/>
-      <c r="AZ58" s="2"/>
-      <c r="BA58" s="2"/>
-      <c r="BB58" s="2"/>
-      <c r="BC58" s="2"/>
-      <c r="BD58" s="2"/>
-      <c r="BE58" s="2"/>
-      <c r="BF58" s="2"/>
-      <c r="BG58" s="2"/>
-      <c r="BH58" s="2"/>
-      <c r="BI58" s="2"/>
-      <c r="BJ58" s="2"/>
-      <c r="BK58" s="2"/>
-      <c r="BL58" s="2"/>
-      <c r="BM58" s="2"/>
-      <c r="BN58" s="2"/>
-      <c r="BO58" s="2"/>
-      <c r="BP58" s="2"/>
-      <c r="BQ58" s="2"/>
-      <c r="BR58" s="2"/>
-      <c r="BS58" s="2"/>
-      <c r="BT58" s="2"/>
-      <c r="BU58" s="2"/>
-    </row>
-    <row r="59" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>57</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
-      <c r="W59" s="2"/>
-      <c r="X59" s="2"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
-      <c r="AA59" s="2"/>
-      <c r="AB59" s="2"/>
-      <c r="AC59" s="2"/>
-      <c r="AD59" s="2"/>
-      <c r="AE59" s="2"/>
-      <c r="AF59" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG59" s="2"/>
-      <c r="AH59" s="2"/>
-      <c r="AI59" s="2"/>
-      <c r="AJ59" s="2"/>
-      <c r="AK59" s="2"/>
-      <c r="AL59" s="2"/>
-      <c r="AM59" s="2"/>
-      <c r="AN59" s="2"/>
-      <c r="AO59" s="2"/>
-      <c r="AP59" s="2"/>
-      <c r="AQ59" s="2"/>
-      <c r="AR59" s="2"/>
-      <c r="AS59" s="2"/>
-      <c r="AT59" s="2"/>
-      <c r="AU59" s="2"/>
-      <c r="AV59" s="2"/>
-      <c r="AW59" s="2"/>
-      <c r="AX59" s="2"/>
-      <c r="AY59" s="2"/>
-      <c r="AZ59" s="2"/>
-      <c r="BA59" s="2"/>
-      <c r="BB59" s="2"/>
-      <c r="BC59" s="2"/>
-      <c r="BD59" s="2"/>
-      <c r="BE59" s="2"/>
-      <c r="BF59" s="2"/>
-      <c r="BG59" s="2"/>
-      <c r="BH59" s="2">
-        <v>1</v>
-      </c>
-      <c r="BI59" s="2">
-        <v>1</v>
-      </c>
-      <c r="BJ59" s="2"/>
-      <c r="BK59" s="2"/>
-      <c r="BL59" s="2"/>
-      <c r="BM59" s="2"/>
-      <c r="BN59" s="2"/>
-      <c r="BO59" s="2"/>
-      <c r="BP59" s="2"/>
-      <c r="BQ59" s="2"/>
-      <c r="BR59" s="2"/>
-      <c r="BS59" s="2"/>
-      <c r="BT59" s="2"/>
-      <c r="BU59" s="2"/>
-    </row>
-    <row r="60" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>58</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
-      <c r="AB60" s="3"/>
-      <c r="AC60" s="3"/>
-      <c r="AD60" s="3"/>
-      <c r="AE60" s="3"/>
-      <c r="AF60" s="3"/>
-      <c r="AG60" s="3"/>
-      <c r="AH60" s="3"/>
-      <c r="AI60" s="3"/>
-      <c r="AJ60" s="3"/>
-      <c r="AK60" s="3"/>
-      <c r="AL60" s="3"/>
-      <c r="AM60" s="3"/>
-      <c r="AN60" s="3"/>
-      <c r="AO60" s="3"/>
-      <c r="AP60" s="3"/>
-      <c r="AQ60" s="3"/>
-      <c r="AR60" s="3"/>
-      <c r="AS60" s="3"/>
-      <c r="AT60" s="3"/>
-      <c r="AU60" s="3"/>
-      <c r="AV60" s="3"/>
-      <c r="AW60" s="3"/>
-      <c r="AX60" s="3"/>
-      <c r="AY60" s="3"/>
-      <c r="AZ60" s="3"/>
-      <c r="BA60" s="3"/>
-      <c r="BB60" s="3"/>
-      <c r="BC60" s="3"/>
-      <c r="BD60" s="3"/>
-      <c r="BE60" s="3"/>
-      <c r="BF60" s="3"/>
-      <c r="BG60" s="3"/>
-      <c r="BH60" s="3"/>
-      <c r="BI60" s="3">
-        <v>1</v>
-      </c>
-      <c r="BJ60" s="3"/>
-      <c r="BK60" s="3"/>
-      <c r="BL60" s="3"/>
-      <c r="BM60" s="3"/>
-      <c r="BN60" s="3"/>
-      <c r="BO60" s="3"/>
-      <c r="BP60" s="3"/>
-      <c r="BQ60" s="3"/>
-      <c r="BR60" s="3"/>
-      <c r="BS60" s="3"/>
-      <c r="BT60" s="3"/>
-      <c r="BU60" s="3"/>
-    </row>
-    <row r="61" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>59</v>
-      </c>
-      <c r="B61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>60</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1</v>
-      </c>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
-      <c r="AB62" s="3"/>
-      <c r="AC62" s="3"/>
-      <c r="AD62" s="3"/>
-      <c r="AE62" s="3"/>
-      <c r="AF62" s="3"/>
-      <c r="AG62" s="3"/>
-      <c r="AH62" s="3"/>
-      <c r="AI62" s="3"/>
-      <c r="AJ62" s="3"/>
-      <c r="AK62" s="3"/>
-      <c r="AL62" s="3"/>
-      <c r="AM62" s="3"/>
-      <c r="AN62" s="3"/>
-      <c r="AO62" s="3"/>
-      <c r="AP62" s="3"/>
-      <c r="AQ62" s="3"/>
-      <c r="AR62" s="3"/>
-      <c r="AS62" s="3"/>
-      <c r="AT62" s="3"/>
-      <c r="AU62" s="3"/>
-      <c r="AV62" s="3"/>
-      <c r="AW62" s="3"/>
-      <c r="AX62" s="3"/>
-      <c r="AY62" s="3"/>
-      <c r="AZ62" s="3"/>
-      <c r="BA62" s="3"/>
-      <c r="BB62" s="3"/>
-      <c r="BC62" s="3"/>
-      <c r="BD62" s="3"/>
-      <c r="BE62" s="3"/>
-      <c r="BF62" s="3"/>
-      <c r="BG62" s="3"/>
-      <c r="BH62" s="3"/>
-      <c r="BI62" s="3"/>
-      <c r="BJ62" s="3"/>
-      <c r="BK62" s="3"/>
-      <c r="BL62" s="3"/>
-      <c r="BM62" s="3"/>
-      <c r="BN62" s="3"/>
-      <c r="BO62" s="3"/>
-      <c r="BP62" s="3"/>
-      <c r="BQ62" s="3"/>
-      <c r="BR62" s="3"/>
-      <c r="BS62" s="3"/>
-      <c r="BT62" s="3"/>
-      <c r="BU62" s="3"/>
-    </row>
-    <row r="63" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>61</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -5324,9 +5090,7 @@
       <c r="BG63" s="2"/>
       <c r="BH63" s="2"/>
       <c r="BI63" s="2"/>
-      <c r="BJ63" s="2">
-        <v>1</v>
-      </c>
+      <c r="BJ63" s="2"/>
       <c r="BK63" s="2"/>
       <c r="BL63" s="2"/>
       <c r="BM63" s="2"/>
@@ -5335,558 +5099,429 @@
       <c r="BP63" s="2"/>
       <c r="BQ63" s="2"/>
       <c r="BR63" s="2"/>
-      <c r="BS63" s="2"/>
-      <c r="BT63" s="2"/>
-      <c r="BU63" s="2"/>
-    </row>
-    <row r="64" spans="1:73" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A64">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="65" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <v>66</v>
+      </c>
+      <c r="B65" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:70" x14ac:dyDescent="0.45">
+      <c r="A66">
         <v>67</v>
       </c>
-      <c r="Q64">
-        <v>1</v>
-      </c>
-      <c r="BM64">
-        <v>1</v>
-      </c>
-      <c r="BN64">
-        <v>1</v>
-      </c>
-      <c r="BO64">
-        <v>1</v>
-      </c>
-      <c r="BP64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>63</v>
-      </c>
-      <c r="B65" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="66" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>64</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" s="2"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="2"/>
-      <c r="T66" s="2"/>
-      <c r="U66" s="2"/>
-      <c r="V66" s="2"/>
-      <c r="W66" s="2"/>
-      <c r="X66" s="2"/>
-      <c r="Y66" s="2"/>
-      <c r="Z66" s="2"/>
-      <c r="AA66" s="2"/>
-      <c r="AB66" s="2"/>
-      <c r="AC66" s="2"/>
-      <c r="AD66" s="2"/>
-      <c r="AE66" s="2"/>
-      <c r="AF66" s="2"/>
-      <c r="AG66" s="2"/>
-      <c r="AH66" s="2"/>
-      <c r="AI66" s="2"/>
-      <c r="AJ66" s="2"/>
-      <c r="AK66" s="2"/>
-      <c r="AL66" s="2"/>
-      <c r="AM66" s="2"/>
-      <c r="AN66" s="2"/>
-      <c r="AO66" s="2"/>
-      <c r="AP66" s="2"/>
-      <c r="AQ66" s="2"/>
-      <c r="AR66" s="2"/>
-      <c r="AS66" s="2"/>
-      <c r="AT66" s="2"/>
-      <c r="AU66" s="2"/>
-      <c r="AV66" s="2"/>
-      <c r="AW66" s="2"/>
-      <c r="AX66" s="2"/>
-      <c r="AY66" s="2"/>
-      <c r="AZ66" s="2"/>
-      <c r="BA66" s="2"/>
-      <c r="BB66" s="2"/>
-      <c r="BC66" s="2"/>
-      <c r="BD66" s="2"/>
-      <c r="BE66" s="2"/>
-      <c r="BF66" s="2"/>
-      <c r="BG66" s="2"/>
-      <c r="BH66" s="2"/>
-      <c r="BI66" s="2"/>
-      <c r="BJ66" s="2"/>
-      <c r="BK66" s="2"/>
-      <c r="BL66" s="2"/>
-      <c r="BM66" s="2"/>
-      <c r="BN66" s="2"/>
-      <c r="BO66" s="2"/>
-      <c r="BP66" s="2"/>
-      <c r="BQ66" s="2"/>
-      <c r="BR66" s="2"/>
-      <c r="BS66" s="2"/>
-      <c r="BT66" s="2"/>
-      <c r="BU66" s="2"/>
-    </row>
-    <row r="67" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:73" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="AC67">
+        <v>1</v>
+      </c>
+      <c r="AI67">
+        <v>1</v>
+      </c>
+      <c r="BN67">
+        <v>1</v>
+      </c>
+      <c r="BQ67">
+        <v>1</v>
+      </c>
+      <c r="BR67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68">
-        <v>66</v>
-      </c>
-      <c r="B68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:73" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+      <c r="Y68" s="2"/>
+      <c r="Z68" s="2"/>
+      <c r="AA68" s="2"/>
+      <c r="AB68" s="2"/>
+      <c r="AC68" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD68" s="2"/>
+      <c r="AE68" s="2"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="2"/>
+      <c r="AH68" s="2"/>
+      <c r="AI68" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ68" s="2"/>
+      <c r="AK68" s="2"/>
+      <c r="AL68" s="2"/>
+      <c r="AM68" s="2"/>
+      <c r="AN68" s="2"/>
+      <c r="AO68" s="2"/>
+      <c r="AP68" s="2">
+        <v>1</v>
+      </c>
+      <c r="AQ68" s="2"/>
+      <c r="AR68" s="2"/>
+      <c r="AS68" s="2"/>
+      <c r="AT68" s="2"/>
+      <c r="AU68" s="2"/>
+      <c r="AV68" s="2"/>
+      <c r="AW68" s="2"/>
+      <c r="AX68" s="2"/>
+      <c r="AY68" s="2"/>
+      <c r="AZ68" s="2"/>
+      <c r="BA68" s="2"/>
+      <c r="BB68" s="2"/>
+      <c r="BC68" s="2"/>
+      <c r="BD68" s="2"/>
+      <c r="BE68" s="2"/>
+      <c r="BF68" s="2"/>
+      <c r="BG68" s="2"/>
+      <c r="BH68" s="2"/>
+      <c r="BI68" s="2"/>
+      <c r="BJ68" s="2"/>
+      <c r="BK68" s="2"/>
+      <c r="BL68" s="2"/>
+      <c r="BM68" s="2"/>
+      <c r="BN68" s="2">
+        <v>1</v>
+      </c>
+      <c r="BO68" s="2"/>
+      <c r="BP68" s="2"/>
+      <c r="BQ68" s="2">
+        <v>1</v>
+      </c>
+      <c r="BR68" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:70" x14ac:dyDescent="0.45">
       <c r="A69">
-        <v>67</v>
-      </c>
-      <c r="B69" t="s">
-        <v>30</v>
-      </c>
-      <c r="BT69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="2"/>
+      <c r="U69" s="2">
+        <v>1</v>
+      </c>
+      <c r="V69" s="2"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="2"/>
+      <c r="Y69" s="2"/>
+      <c r="Z69" s="2"/>
+      <c r="AA69" s="2"/>
+      <c r="AB69" s="2"/>
+      <c r="AC69" s="2">
+        <v>1</v>
+      </c>
+      <c r="AD69" s="2"/>
+      <c r="AE69" s="2"/>
+      <c r="AF69" s="2"/>
+      <c r="AG69" s="2"/>
+      <c r="AH69" s="2"/>
+      <c r="AI69" s="2"/>
+      <c r="AJ69" s="2"/>
+      <c r="AK69" s="2"/>
+      <c r="AL69" s="2"/>
+      <c r="AM69" s="2"/>
+      <c r="AN69" s="2"/>
+      <c r="AO69" s="2"/>
+      <c r="AP69" s="2"/>
+      <c r="AQ69" s="2"/>
+      <c r="AR69" s="2"/>
+      <c r="AS69" s="2"/>
+      <c r="AT69" s="2"/>
+      <c r="AU69" s="2"/>
+      <c r="AV69" s="2"/>
+      <c r="AW69" s="2"/>
+      <c r="AX69" s="2"/>
+      <c r="AY69" s="2"/>
+      <c r="AZ69" s="2"/>
+      <c r="BA69" s="2"/>
+      <c r="BB69" s="2"/>
+      <c r="BC69" s="2"/>
+      <c r="BD69" s="2"/>
+      <c r="BE69" s="2"/>
+      <c r="BF69" s="2"/>
+      <c r="BG69" s="2"/>
+      <c r="BH69" s="2"/>
+      <c r="BI69" s="2"/>
+      <c r="BJ69" s="2"/>
+      <c r="BK69" s="2"/>
+      <c r="BL69" s="2"/>
+      <c r="BM69" s="2"/>
+      <c r="BN69" s="2"/>
+      <c r="BO69" s="2"/>
+      <c r="BP69" s="2"/>
+      <c r="BQ69" s="2"/>
+      <c r="BR69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:70" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70">
-        <v>68</v>
-      </c>
-      <c r="B70" t="s">
-        <v>28</v>
-      </c>
-      <c r="V70">
-        <v>1</v>
-      </c>
-      <c r="AF70">
-        <v>1</v>
-      </c>
-      <c r="AL70">
-        <v>1</v>
-      </c>
-      <c r="BQ70">
-        <v>1</v>
-      </c>
-      <c r="BT70">
-        <v>1</v>
-      </c>
-      <c r="BU70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>69</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-      <c r="T71" s="2"/>
-      <c r="U71" s="2"/>
-      <c r="V71" s="2">
-        <v>1</v>
-      </c>
-      <c r="W71" s="2"/>
-      <c r="X71" s="2"/>
-      <c r="Y71" s="2"/>
-      <c r="Z71" s="2"/>
-      <c r="AA71" s="2"/>
-      <c r="AB71" s="2"/>
-      <c r="AC71" s="2"/>
-      <c r="AD71" s="2"/>
-      <c r="AE71" s="2"/>
-      <c r="AF71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG71" s="2"/>
-      <c r="AH71" s="2"/>
-      <c r="AI71" s="2"/>
-      <c r="AJ71" s="2"/>
-      <c r="AK71" s="2"/>
-      <c r="AL71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM71" s="2"/>
-      <c r="AN71" s="2"/>
-      <c r="AO71" s="2"/>
-      <c r="AP71" s="2"/>
-      <c r="AQ71" s="2"/>
-      <c r="AR71" s="2"/>
-      <c r="AS71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT71" s="2"/>
-      <c r="AU71" s="2"/>
-      <c r="AV71" s="2"/>
-      <c r="AW71" s="2"/>
-      <c r="AX71" s="2"/>
-      <c r="AY71" s="2"/>
-      <c r="AZ71" s="2"/>
-      <c r="BA71" s="2"/>
-      <c r="BB71" s="2"/>
-      <c r="BC71" s="2"/>
-      <c r="BD71" s="2"/>
-      <c r="BE71" s="2"/>
-      <c r="BF71" s="2"/>
-      <c r="BG71" s="2"/>
-      <c r="BH71" s="2"/>
-      <c r="BI71" s="2"/>
-      <c r="BJ71" s="2"/>
-      <c r="BK71" s="2"/>
-      <c r="BL71" s="2"/>
-      <c r="BM71" s="2"/>
-      <c r="BN71" s="2"/>
-      <c r="BO71" s="2"/>
-      <c r="BP71" s="2"/>
-      <c r="BQ71" s="2">
-        <v>1</v>
-      </c>
-      <c r="BR71" s="2"/>
-      <c r="BS71" s="2"/>
-      <c r="BT71" s="2">
-        <v>1</v>
-      </c>
-      <c r="BU71" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>70</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-      <c r="T72" s="2"/>
-      <c r="U72" s="2"/>
-      <c r="V72" s="2">
-        <v>1</v>
-      </c>
-      <c r="W72" s="2"/>
-      <c r="X72" s="2"/>
-      <c r="Y72" s="2"/>
-      <c r="Z72" s="2"/>
-      <c r="AA72" s="2"/>
-      <c r="AB72" s="2"/>
-      <c r="AC72" s="2"/>
-      <c r="AD72" s="2"/>
-      <c r="AE72" s="2"/>
-      <c r="AF72" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG72" s="2"/>
-      <c r="AH72" s="2"/>
-      <c r="AI72" s="2"/>
-      <c r="AJ72" s="2"/>
-      <c r="AK72" s="2"/>
-      <c r="AL72" s="2"/>
-      <c r="AM72" s="2"/>
-      <c r="AN72" s="2"/>
-      <c r="AO72" s="2"/>
-      <c r="AP72" s="2"/>
-      <c r="AQ72" s="2"/>
-      <c r="AR72" s="2"/>
-      <c r="AS72" s="2"/>
-      <c r="AT72" s="2"/>
-      <c r="AU72" s="2"/>
-      <c r="AV72" s="2"/>
-      <c r="AW72" s="2"/>
-      <c r="AX72" s="2"/>
-      <c r="AY72" s="2"/>
-      <c r="AZ72" s="2"/>
-      <c r="BA72" s="2"/>
-      <c r="BB72" s="2"/>
-      <c r="BC72" s="2"/>
-      <c r="BD72" s="2"/>
-      <c r="BE72" s="2"/>
-      <c r="BF72" s="2"/>
-      <c r="BG72" s="2"/>
-      <c r="BH72" s="2"/>
-      <c r="BI72" s="2"/>
-      <c r="BJ72" s="2"/>
-      <c r="BK72" s="2"/>
-      <c r="BL72" s="2"/>
-      <c r="BM72" s="2"/>
-      <c r="BN72" s="2"/>
-      <c r="BO72" s="2"/>
-      <c r="BP72" s="2"/>
-      <c r="BQ72" s="2"/>
-      <c r="BR72" s="2"/>
-      <c r="BS72" s="2"/>
-      <c r="BT72" s="2"/>
-      <c r="BU72" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:73" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-      <c r="AA73" s="3"/>
-      <c r="AB73" s="3"/>
-      <c r="AC73" s="3"/>
-      <c r="AD73" s="3"/>
-      <c r="AE73" s="3"/>
-      <c r="AF73" s="3"/>
-      <c r="AG73" s="3"/>
-      <c r="AH73" s="3"/>
-      <c r="AI73" s="3"/>
-      <c r="AJ73" s="3"/>
-      <c r="AK73" s="3"/>
-      <c r="AL73" s="3"/>
-      <c r="AM73" s="3"/>
-      <c r="AN73" s="3"/>
-      <c r="AO73" s="3"/>
-      <c r="AP73" s="3"/>
-      <c r="AQ73" s="3"/>
-      <c r="AR73" s="3"/>
-      <c r="AS73" s="3"/>
-      <c r="AT73" s="3"/>
-      <c r="AU73" s="3"/>
-      <c r="AV73" s="3"/>
-      <c r="AW73" s="3"/>
-      <c r="AX73" s="3"/>
-      <c r="AY73" s="3"/>
-      <c r="AZ73" s="3"/>
-      <c r="BA73" s="3"/>
-      <c r="BB73" s="3"/>
-      <c r="BC73" s="3"/>
-      <c r="BD73" s="3"/>
-      <c r="BE73" s="3"/>
-      <c r="BF73" s="3"/>
-      <c r="BG73" s="3"/>
-      <c r="BH73" s="3"/>
-      <c r="BI73" s="3"/>
-      <c r="BJ73" s="3"/>
-      <c r="BK73" s="3"/>
-      <c r="BL73" s="3"/>
-      <c r="BM73" s="3"/>
-      <c r="BN73" s="3"/>
-      <c r="BO73" s="3"/>
-      <c r="BP73" s="3"/>
-      <c r="BQ73" s="3"/>
-      <c r="BR73" s="3"/>
-      <c r="BS73" s="3"/>
-      <c r="BT73" s="3"/>
-      <c r="BU73" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+      <c r="K70" s="3"/>
+      <c r="L70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
+      <c r="Y70" s="3"/>
+      <c r="Z70" s="3"/>
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="3"/>
+      <c r="AC70" s="3"/>
+      <c r="AD70" s="3"/>
+      <c r="AE70" s="3"/>
+      <c r="AF70" s="3"/>
+      <c r="AG70" s="3"/>
+      <c r="AH70" s="3"/>
+      <c r="AI70" s="3"/>
+      <c r="AJ70" s="3"/>
+      <c r="AK70" s="3"/>
+      <c r="AL70" s="3"/>
+      <c r="AM70" s="3"/>
+      <c r="AN70" s="3"/>
+      <c r="AO70" s="3"/>
+      <c r="AP70" s="3"/>
+      <c r="AQ70" s="3"/>
+      <c r="AR70" s="3"/>
+      <c r="AS70" s="3"/>
+      <c r="AT70" s="3"/>
+      <c r="AU70" s="3"/>
+      <c r="AV70" s="3"/>
+      <c r="AW70" s="3"/>
+      <c r="AX70" s="3"/>
+      <c r="AY70" s="3"/>
+      <c r="AZ70" s="3"/>
+      <c r="BA70" s="3"/>
+      <c r="BB70" s="3"/>
+      <c r="BC70" s="3"/>
+      <c r="BD70" s="3"/>
+      <c r="BE70" s="3"/>
+      <c r="BF70" s="3"/>
+      <c r="BG70" s="3"/>
+      <c r="BH70" s="3"/>
+      <c r="BI70" s="3"/>
+      <c r="BJ70" s="3"/>
+      <c r="BK70" s="3"/>
+      <c r="BL70" s="3"/>
+      <c r="BM70" s="3"/>
+      <c r="BN70" s="3"/>
+      <c r="BO70" s="3"/>
+      <c r="BP70" s="3"/>
+      <c r="BQ70" s="3"/>
+      <c r="BR70" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:BU73" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}"/>
+  <autoFilter ref="B2:BR70" xr:uid="{7DD69CEB-FB4B-428B-8D1B-77C5ED66F830}"/>
   <conditionalFormatting sqref="B5:D6">
-    <cfRule type="duplicateValues" dxfId="69" priority="1572"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="1572"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:D7">
-    <cfRule type="duplicateValues" dxfId="68" priority="1566"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="1573"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="1566"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="1573"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:D8">
-    <cfRule type="duplicateValues" dxfId="66" priority="1567"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="1574"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="1567"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="1574"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B9:D9">
-    <cfRule type="duplicateValues" dxfId="64" priority="1575"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="1575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B10:D10">
-    <cfRule type="duplicateValues" dxfId="63" priority="1576"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="1576"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:D11">
-    <cfRule type="duplicateValues" dxfId="62" priority="1577"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="1577"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:D12">
-    <cfRule type="duplicateValues" dxfId="61" priority="1578"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="1578"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13:D13">
-    <cfRule type="duplicateValues" dxfId="60" priority="1579"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="1579"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B14:D14">
-    <cfRule type="duplicateValues" dxfId="59" priority="1580"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="1580"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:D15">
-    <cfRule type="duplicateValues" dxfId="58" priority="1581"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="1582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:D16">
-    <cfRule type="duplicateValues" dxfId="57" priority="1582"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="1583"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B17:D17">
-    <cfRule type="duplicateValues" dxfId="56" priority="1583"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="1584"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:D18">
-    <cfRule type="duplicateValues" dxfId="55" priority="1584"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="1585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:D19">
-    <cfRule type="duplicateValues" dxfId="54" priority="1585"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:D20">
     <cfRule type="duplicateValues" dxfId="53" priority="1586"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:D28">
-    <cfRule type="duplicateValues" dxfId="52" priority="1588"/>
+  <conditionalFormatting sqref="B26:D26">
+    <cfRule type="duplicateValues" dxfId="52" priority="1589"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:D29">
-    <cfRule type="duplicateValues" dxfId="51" priority="1589"/>
+  <conditionalFormatting sqref="B27:D35">
+    <cfRule type="duplicateValues" dxfId="51" priority="1590"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30:D38">
-    <cfRule type="duplicateValues" dxfId="50" priority="1590"/>
+  <conditionalFormatting sqref="B34:D34">
+    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37:D37">
-    <cfRule type="duplicateValues" dxfId="49" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="1"/>
+  <conditionalFormatting sqref="B36:D43">
+    <cfRule type="duplicateValues" dxfId="48" priority="1591"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B39:D46">
-    <cfRule type="duplicateValues" dxfId="47" priority="1591"/>
+  <conditionalFormatting sqref="B44:D44">
+    <cfRule type="duplicateValues" dxfId="47" priority="1592"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47:D47">
-    <cfRule type="duplicateValues" dxfId="46" priority="1592"/>
+  <conditionalFormatting sqref="B45:D45">
+    <cfRule type="duplicateValues" dxfId="46" priority="1593"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48:D48">
-    <cfRule type="duplicateValues" dxfId="45" priority="1593"/>
+  <conditionalFormatting sqref="B46:D49">
+    <cfRule type="duplicateValues" dxfId="45" priority="1568"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1570"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49:D52">
-    <cfRule type="duplicateValues" dxfId="44" priority="1570"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="1568"/>
+  <conditionalFormatting sqref="B50:D50">
+    <cfRule type="duplicateValues" dxfId="43" priority="1594"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B53:D53">
-    <cfRule type="duplicateValues" dxfId="42" priority="1594"/>
+  <conditionalFormatting sqref="B51:D70">
+    <cfRule type="duplicateValues" dxfId="42" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="1619"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:D73">
-    <cfRule type="duplicateValues" dxfId="41" priority="1595"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="1619"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:BU4 B5:D73">
-    <cfRule type="duplicateValues" dxfId="39" priority="1627"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:BU4">
-    <cfRule type="duplicateValues" dxfId="38" priority="1623"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:BV1048576">
-    <cfRule type="cellIs" dxfId="37" priority="9" operator="equal">
+  <conditionalFormatting sqref="E5:BS1048576">
+    <cfRule type="cellIs" dxfId="40" priority="9" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="36" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AI4">
-    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
+  <conditionalFormatting sqref="AE2:AF4">
+    <cfRule type="duplicateValues" dxfId="38" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI4">
-    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
+  <conditionalFormatting sqref="AF2:AF4">
+    <cfRule type="duplicateValues" dxfId="37" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ2:AJ4">
-    <cfRule type="duplicateValues" dxfId="33" priority="4"/>
+  <conditionalFormatting sqref="AG2:AG4">
+    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK4">
-    <cfRule type="duplicateValues" dxfId="32" priority="3"/>
+  <conditionalFormatting sqref="AH2:AH4">
+    <cfRule type="duplicateValues" dxfId="35" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:BR4">
+    <cfRule type="duplicateValues" dxfId="34" priority="1643"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20:D25">
+    <cfRule type="duplicateValues" dxfId="1" priority="1646"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:BR4 B5:D70">
+    <cfRule type="duplicateValues" dxfId="0" priority="1651"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F02EE0-40BA-4311-B39A-384F2CBD26CC}">
   <dimension ref="A1:BT72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="32" max="32" width="13.85546875" customWidth="1"/>
-    <col min="53" max="53" width="13.85546875" customWidth="1"/>
-    <col min="57" max="60" width="10.85546875" customWidth="1"/>
-    <col min="61" max="61" width="13.5703125" customWidth="1"/>
-    <col min="62" max="62" width="13.28515625" customWidth="1"/>
-    <col min="63" max="63" width="13.42578125" customWidth="1"/>
-    <col min="64" max="73" width="10.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.59765625" customWidth="1"/>
+    <col min="32" max="32" width="13.86328125" customWidth="1"/>
+    <col min="53" max="53" width="13.86328125" customWidth="1"/>
+    <col min="57" max="60" width="10.86328125" customWidth="1"/>
+    <col min="61" max="61" width="13.59765625" customWidth="1"/>
+    <col min="62" max="62" width="13.265625" customWidth="1"/>
+    <col min="63" max="63" width="13.3984375" customWidth="1"/>
+    <col min="64" max="73" width="10.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:72" ht="57.4" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6101,7 +5736,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>60</v>
       </c>
@@ -6271,7 +5906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -6318,7 +5953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -6356,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -6385,7 +6020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -6405,7 +6040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -6517,7 +6152,7 @@
       </c>
       <c r="BT7" s="2"/>
     </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -6609,7 +6244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -6662,7 +6297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6679,7 +6314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -6708,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:72" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:72" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
@@ -6800,7 +6435,7 @@
       <c r="BS12" s="3"/>
       <c r="BT12" s="3"/>
     </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -6920,7 +6555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -7000,7 +6635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -7077,7 +6712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -7094,7 +6729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -7114,12 +6749,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -7178,7 +6813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -7204,7 +6839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>64</v>
       </c>
@@ -7284,7 +6919,7 @@
       <c r="BS21" s="3"/>
       <c r="BT21" s="3"/>
     </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>16</v>
       </c>
@@ -7392,12 +7027,12 @@
       <c r="BS22" s="2"/>
       <c r="BT22" s="2"/>
     </row>
-    <row r="23" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
         <v>69</v>
       </c>
@@ -7477,7 +7112,7 @@
       <c r="BS24" s="3"/>
       <c r="BT24" s="3"/>
     </row>
-    <row r="25" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -7589,7 +7224,7 @@
       <c r="BS25" s="2"/>
       <c r="BT25" s="2"/>
     </row>
-    <row r="26" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>19</v>
       </c>
@@ -7697,7 +7332,7 @@
       <c r="BS26" s="2"/>
       <c r="BT26" s="2"/>
     </row>
-    <row r="27" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>65</v>
       </c>
@@ -7773,7 +7408,7 @@
       <c r="BS27" s="3"/>
       <c r="BT27" s="3"/>
     </row>
-    <row r="28" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -7857,7 +7492,7 @@
       <c r="BS28" s="2"/>
       <c r="BT28" s="2"/>
     </row>
-    <row r="29" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -7865,7 +7500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
@@ -7941,7 +7576,7 @@
       <c r="BS30" s="3"/>
       <c r="BT30" s="3"/>
     </row>
-    <row r="31" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" s="2" t="s">
         <v>23</v>
       </c>
@@ -8025,7 +7660,7 @@
       <c r="BS31" s="2"/>
       <c r="BT31" s="2"/>
     </row>
-    <row r="32" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>24</v>
       </c>
@@ -8113,7 +7748,7 @@
       <c r="BS32" s="2"/>
       <c r="BT32" s="2"/>
     </row>
-    <row r="33" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -8136,7 +7771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -8156,7 +7791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>27</v>
       </c>
@@ -8246,7 +7881,7 @@
       <c r="BS35" s="2"/>
       <c r="BT35" s="2"/>
     </row>
-    <row r="36" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>73</v>
       </c>
@@ -8328,7 +7963,7 @@
       <c r="BS36" s="3"/>
       <c r="BT36" s="3"/>
     </row>
-    <row r="37" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
         <v>28</v>
       </c>
@@ -8416,7 +8051,7 @@
       <c r="BS37" s="2"/>
       <c r="BT37" s="2"/>
     </row>
-    <row r="38" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -8439,7 +8074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -8447,7 +8082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" s="3" t="s">
         <v>31</v>
       </c>
@@ -8531,7 +8166,7 @@
       <c r="BS40" s="3"/>
       <c r="BT40" s="3"/>
     </row>
-    <row r="41" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -8545,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -8559,7 +8194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>70</v>
       </c>
@@ -8573,7 +8208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" s="5" t="s">
         <v>34</v>
       </c>
@@ -8659,7 +8294,7 @@
       <c r="BS44" s="5"/>
       <c r="BT44" s="5"/>
     </row>
-    <row r="45" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" s="3" t="s">
         <v>71</v>
       </c>
@@ -8753,7 +8388,7 @@
       <c r="BS45" s="3"/>
       <c r="BT45" s="3"/>
     </row>
-    <row r="46" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" s="2" t="s">
         <v>44</v>
       </c>
@@ -8845,7 +8480,7 @@
       <c r="BS46" s="2"/>
       <c r="BT46" s="2"/>
     </row>
-    <row r="47" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
         <v>36</v>
       </c>
@@ -8929,7 +8564,7 @@
       <c r="BS47" s="2"/>
       <c r="BT47" s="2"/>
     </row>
-    <row r="48" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
@@ -9009,7 +8644,7 @@
       <c r="BS48" s="3"/>
       <c r="BT48" s="3"/>
     </row>
-    <row r="49" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
         <v>37</v>
       </c>
@@ -9095,12 +8730,12 @@
       <c r="BS49" s="2"/>
       <c r="BT49" s="2"/>
     </row>
-    <row r="50" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -9108,7 +8743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
@@ -9184,7 +8819,7 @@
       <c r="BS52" s="3"/>
       <c r="BT52" s="3"/>
     </row>
-    <row r="53" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
         <v>41</v>
       </c>
@@ -9260,7 +8895,7 @@
       <c r="BS53" s="2"/>
       <c r="BT53" s="2"/>
     </row>
-    <row r="54" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>72</v>
       </c>
@@ -9268,7 +8903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -9279,7 +8914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A56" s="2" t="s">
         <v>43</v>
       </c>
@@ -9365,7 +9000,7 @@
       <c r="BS56" s="2"/>
       <c r="BT56" s="2"/>
     </row>
-    <row r="57" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
         <v>45</v>
       </c>
@@ -9441,7 +9076,7 @@
       <c r="BS57" s="2"/>
       <c r="BT57" s="2"/>
     </row>
-    <row r="58" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" s="3" t="s">
         <v>46</v>
       </c>
@@ -9517,12 +9152,12 @@
       <c r="BS58" s="3"/>
       <c r="BT58" s="3"/>
     </row>
-    <row r="59" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A60" s="3" t="s">
         <v>48</v>
       </c>
@@ -9600,7 +9235,7 @@
       <c r="BS60" s="3"/>
       <c r="BT60" s="3"/>
     </row>
-    <row r="61" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
         <v>49</v>
       </c>
@@ -9678,7 +9313,7 @@
       <c r="BS61" s="2"/>
       <c r="BT61" s="2"/>
     </row>
-    <row r="62" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -9686,17 +9321,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="64" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
@@ -9782,27 +9417,27 @@
       <c r="BS65" s="2"/>
       <c r="BT65" s="2"/>
     </row>
-    <row r="66" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="68" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="69" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" s="2" t="s">
         <v>57</v>
       </c>
@@ -9884,7 +9519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:72" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>58</v>
       </c>
@@ -9960,7 +9595,7 @@
       <c r="BS71" s="2"/>
       <c r="BT71" s="2"/>
     </row>
-    <row r="72" spans="1:72" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:72" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A72" s="3" t="s">
         <v>68</v>
       </c>
@@ -10040,92 +9675,92 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="31" priority="1406"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1406"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="30" priority="1400"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="1407"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1400"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1407"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="28" priority="1401"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1408"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1401"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1408"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="26" priority="1409"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1409"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="25" priority="1410"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="24" priority="1411"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="1411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="23" priority="1412"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1412"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="22" priority="1413"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1413"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="21" priority="1414"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1414"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="20" priority="1415"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1415"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="19" priority="1416"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1416"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="18" priority="1417"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1417"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="17" priority="1418"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="16" priority="1419"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1419"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="15" priority="1420"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1420"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="14" priority="1421"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18:A27">
-    <cfRule type="duplicateValues" dxfId="13" priority="1422"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1422"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="12" priority="1423"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1423"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29:A36">
-    <cfRule type="duplicateValues" dxfId="11" priority="1424"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1424"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:A44">
-    <cfRule type="duplicateValues" dxfId="10" priority="1425"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A45">
-    <cfRule type="duplicateValues" dxfId="9" priority="1426"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1426"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A46">
-    <cfRule type="duplicateValues" dxfId="8" priority="1427"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1427"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:A50">
-    <cfRule type="duplicateValues" dxfId="7" priority="1402"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="1404"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1402"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1404"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="duplicateValues" dxfId="5" priority="1428"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1428"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52:A72">
-    <cfRule type="duplicateValues" dxfId="4" priority="1429"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1453"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1429"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1453"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:BT1 A2:A72">
-    <cfRule type="duplicateValues" dxfId="2" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:BT1">
-    <cfRule type="duplicateValues" dxfId="1" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:BU1048576">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
